--- a/data/raw/WEGE3.SA.xlsx
+++ b/data/raw/WEGE3.SA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,5022 +468,5002 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45833</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>39.87528610229492</v>
+        <v>40.36156845092773</v>
       </c>
       <c r="C2" t="n">
-        <v>39.96110106785879</v>
+        <v>41.10529566000937</v>
       </c>
       <c r="D2" t="n">
-        <v>39.19830339468341</v>
+        <v>40.27575349316402</v>
       </c>
       <c r="E2" t="n">
-        <v>39.579700412618</v>
+        <v>41.00041030748639</v>
       </c>
       <c r="F2" t="n">
-        <v>4072000</v>
+        <v>4161300</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45834</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>41.06715393066406</v>
+        <v>38.7215461730957</v>
       </c>
       <c r="C3" t="n">
-        <v>41.59157704397158</v>
+        <v>40.7048197022717</v>
       </c>
       <c r="D3" t="n">
-        <v>39.94202612675772</v>
+        <v>38.55944965597681</v>
       </c>
       <c r="E3" t="n">
-        <v>39.94202612675772</v>
+        <v>40.7048197022717</v>
       </c>
       <c r="F3" t="n">
-        <v>11156400</v>
+        <v>11029800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45835</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>40.38063049316406</v>
+        <v>38.24480438232422</v>
       </c>
       <c r="C4" t="n">
-        <v>41.42948025861452</v>
+        <v>38.66434218214748</v>
       </c>
       <c r="D4" t="n">
-        <v>40.38063049316406</v>
+        <v>38.10177823106537</v>
       </c>
       <c r="E4" t="n">
-        <v>40.72389028413674</v>
+        <v>38.6166680108299</v>
       </c>
       <c r="F4" t="n">
-        <v>6984100</v>
+        <v>11678900</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45838</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>40.7906379699707</v>
+        <v>38.04457092285156</v>
       </c>
       <c r="C5" t="n">
-        <v>41.12436440894292</v>
+        <v>38.36876038210561</v>
       </c>
       <c r="D5" t="n">
-        <v>40.26621486564948</v>
+        <v>37.36758459152572</v>
       </c>
       <c r="E5" t="n">
-        <v>40.34249644163367</v>
+        <v>37.60595908693881</v>
       </c>
       <c r="F5" t="n">
-        <v>10282300</v>
+        <v>12622900</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45839</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>40.52366638183594</v>
+        <v>37.90154266357422</v>
       </c>
       <c r="C6" t="n">
-        <v>40.99088201818248</v>
+        <v>38.21619872593338</v>
       </c>
       <c r="D6" t="n">
-        <v>40.39017723925302</v>
+        <v>37.53921243224407</v>
       </c>
       <c r="E6" t="n">
-        <v>40.69529631867292</v>
+        <v>38.00642801769394</v>
       </c>
       <c r="F6" t="n">
-        <v>7110200</v>
+        <v>11076600</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45840</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>40.45691680908203</v>
+        <v>37.69176864624023</v>
       </c>
       <c r="C7" t="n">
-        <v>41.11482906075225</v>
+        <v>38.23526212686726</v>
       </c>
       <c r="D7" t="n">
-        <v>40.15179776738228</v>
+        <v>37.69176864624023</v>
       </c>
       <c r="E7" t="n">
-        <v>40.31389066696395</v>
+        <v>37.73944644833135</v>
       </c>
       <c r="F7" t="n">
-        <v>7025100</v>
+        <v>5026100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45841</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>40.72389221191406</v>
+        <v>37.82526016235352</v>
       </c>
       <c r="C8" t="n">
-        <v>40.95273329583049</v>
+        <v>38.11131244382608</v>
       </c>
       <c r="D8" t="n">
-        <v>40.26621368138684</v>
+        <v>37.39618901475637</v>
       </c>
       <c r="E8" t="n">
-        <v>40.52365853680321</v>
+        <v>37.75851559995814</v>
       </c>
       <c r="F8" t="n">
-        <v>6963500</v>
+        <v>7131200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45842</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>41.00041580200195</v>
+        <v>39.20783615112305</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3627460763724</v>
+        <v>39.37946607952296</v>
       </c>
       <c r="D9" t="n">
-        <v>40.800182086155</v>
+        <v>37.85387075741941</v>
       </c>
       <c r="E9" t="n">
-        <v>40.87646003810826</v>
+        <v>37.9968932728819</v>
       </c>
       <c r="F9" t="n">
-        <v>3488100</v>
+        <v>11531300</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45845</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>40.36156845092773</v>
+        <v>40.13272476196289</v>
       </c>
       <c r="C10" t="n">
-        <v>41.10529566000937</v>
+        <v>40.53319211415354</v>
       </c>
       <c r="D10" t="n">
-        <v>40.27575349316402</v>
+        <v>39.4557421595612</v>
       </c>
       <c r="E10" t="n">
-        <v>41.00041030748639</v>
+        <v>39.47481255309013</v>
       </c>
       <c r="F10" t="n">
-        <v>4161300</v>
+        <v>17894300</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45846</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>38.72154998779297</v>
+        <v>40.39970779418945</v>
       </c>
       <c r="C11" t="n">
-        <v>40.70482371235342</v>
+        <v>40.88599379365919</v>
       </c>
       <c r="D11" t="n">
-        <v>38.55945345470496</v>
+        <v>40.06598496106793</v>
       </c>
       <c r="E11" t="n">
-        <v>40.70482371235342</v>
+        <v>40.27575567749065</v>
       </c>
       <c r="F11" t="n">
-        <v>11029800</v>
+        <v>13711800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45847</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>38.24480438232422</v>
+        <v>40.018310546875</v>
       </c>
       <c r="C12" t="n">
-        <v>38.66434218214748</v>
+        <v>41.04808645232055</v>
       </c>
       <c r="D12" t="n">
-        <v>38.10177823106537</v>
+        <v>39.83714360659125</v>
       </c>
       <c r="E12" t="n">
-        <v>38.6166680108299</v>
+        <v>41.0385530731348</v>
       </c>
       <c r="F12" t="n">
-        <v>11678900</v>
+        <v>7733200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45848</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>38.04457092285156</v>
+        <v>39.39853286743164</v>
       </c>
       <c r="C13" t="n">
-        <v>38.36876038210561</v>
+        <v>40.28528620384996</v>
       </c>
       <c r="D13" t="n">
-        <v>37.36758459152572</v>
+        <v>39.39853286743164</v>
       </c>
       <c r="E13" t="n">
-        <v>37.60595908693881</v>
+        <v>40.04691172927097</v>
       </c>
       <c r="F13" t="n">
-        <v>12622900</v>
+        <v>8965700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45849</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>37.90154647827148</v>
+        <v>36.24245834350586</v>
       </c>
       <c r="C14" t="n">
-        <v>38.21620257230001</v>
+        <v>38.08270982343451</v>
       </c>
       <c r="D14" t="n">
-        <v>37.53921621047369</v>
+        <v>36.24245834350586</v>
       </c>
       <c r="E14" t="n">
-        <v>38.00643184294766</v>
+        <v>37.48200868631847</v>
       </c>
       <c r="F14" t="n">
-        <v>11076600</v>
+        <v>31116000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45852</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>37.69176864624023</v>
+        <v>34.54522705078125</v>
       </c>
       <c r="C15" t="n">
-        <v>38.23526212686726</v>
+        <v>36.80501596180851</v>
       </c>
       <c r="D15" t="n">
-        <v>37.69176864624023</v>
+        <v>34.4022045540841</v>
       </c>
       <c r="E15" t="n">
-        <v>37.73944644833135</v>
+        <v>36.42361899997709</v>
       </c>
       <c r="F15" t="n">
-        <v>5026100</v>
+        <v>30042500</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45853</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>37.82526016235352</v>
+        <v>34.48801803588867</v>
       </c>
       <c r="C16" t="n">
-        <v>38.11131244382608</v>
+        <v>34.89802243265617</v>
       </c>
       <c r="D16" t="n">
-        <v>37.39618901475637</v>
+        <v>34.26871395066748</v>
       </c>
       <c r="E16" t="n">
-        <v>37.75851559995814</v>
+        <v>34.79314071674631</v>
       </c>
       <c r="F16" t="n">
-        <v>7131200</v>
+        <v>19069200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45854</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>39.20782852172852</v>
+        <v>35.18877792358398</v>
       </c>
       <c r="C17" t="n">
-        <v>39.37945841673122</v>
+        <v>35.18877792358398</v>
       </c>
       <c r="D17" t="n">
-        <v>37.85386339149099</v>
+        <v>34.48940977503464</v>
       </c>
       <c r="E17" t="n">
-        <v>37.99688587912294</v>
+        <v>34.58521222922465</v>
       </c>
       <c r="F17" t="n">
-        <v>11531300</v>
+        <v>11133300</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45855</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>40.13272857666016</v>
+        <v>35.04507446289062</v>
       </c>
       <c r="C18" t="n">
-        <v>40.53319596691603</v>
+        <v>36.34800465937124</v>
       </c>
       <c r="D18" t="n">
-        <v>39.45574590990989</v>
+        <v>35.04507446289062</v>
       </c>
       <c r="E18" t="n">
-        <v>39.47481630525149</v>
+        <v>35.59115649539564</v>
       </c>
       <c r="F18" t="n">
-        <v>17894300</v>
+        <v>14293400</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45856</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>40.39970397949219</v>
+        <v>35.30374145507812</v>
       </c>
       <c r="C19" t="n">
-        <v>40.88598993304491</v>
+        <v>35.90730714696772</v>
       </c>
       <c r="D19" t="n">
-        <v>40.06598117788207</v>
+        <v>34.2498998447827</v>
       </c>
       <c r="E19" t="n">
-        <v>40.27575187449742</v>
+        <v>35.11213654748212</v>
       </c>
       <c r="F19" t="n">
-        <v>13711800</v>
+        <v>18990800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45859</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>40.01830291748047</v>
+        <v>35.55283355712891</v>
       </c>
       <c r="C20" t="n">
-        <v>41.04807862660172</v>
+        <v>35.76360334029732</v>
       </c>
       <c r="D20" t="n">
-        <v>39.83713601173577</v>
+        <v>34.39360705896132</v>
       </c>
       <c r="E20" t="n">
-        <v>41.03854524923349</v>
+        <v>35.07381398056749</v>
       </c>
       <c r="F20" t="n">
-        <v>7733200</v>
+        <v>15042800</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45860</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>39.39853286743164</v>
+        <v>35.61989593505859</v>
       </c>
       <c r="C21" t="n">
-        <v>40.28528620384996</v>
+        <v>35.75402083148994</v>
       </c>
       <c r="D21" t="n">
-        <v>39.39853286743164</v>
+        <v>34.81514290184119</v>
       </c>
       <c r="E21" t="n">
-        <v>40.04691172927097</v>
+        <v>35.70611960485436</v>
       </c>
       <c r="F21" t="n">
-        <v>8965700</v>
+        <v>16118400</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45861</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>36.24245452880859</v>
+        <v>35.5145149230957</v>
       </c>
       <c r="C22" t="n">
-        <v>38.08270581504171</v>
+        <v>36.20430435681071</v>
       </c>
       <c r="D22" t="n">
-        <v>36.24245452880859</v>
+        <v>35.46661369122766</v>
       </c>
       <c r="E22" t="n">
-        <v>37.48200474115242</v>
+        <v>35.84024841628004</v>
       </c>
       <c r="F22" t="n">
-        <v>31116000</v>
+        <v>6629900</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45862</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>34.54522705078125</v>
+        <v>35.57199096679688</v>
       </c>
       <c r="C23" t="n">
-        <v>36.80501596180851</v>
+        <v>35.84024073144381</v>
       </c>
       <c r="D23" t="n">
-        <v>34.4022045540841</v>
+        <v>35.38038242577951</v>
       </c>
       <c r="E23" t="n">
-        <v>36.42361899997709</v>
+        <v>35.51450730810298</v>
       </c>
       <c r="F23" t="n">
-        <v>30042500</v>
+        <v>5735100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45863</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>34.48802185058594</v>
+        <v>36.55877304077148</v>
       </c>
       <c r="C24" t="n">
-        <v>34.89802629270376</v>
+        <v>36.61625670421625</v>
       </c>
       <c r="D24" t="n">
-        <v>34.26871774110767</v>
+        <v>35.75402002569104</v>
       </c>
       <c r="E24" t="n">
-        <v>34.793144565193</v>
+        <v>35.83066491028406</v>
       </c>
       <c r="F24" t="n">
-        <v>19069200</v>
+        <v>9789400</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45866</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>35.18877792358398</v>
+        <v>37.36352920532227</v>
       </c>
       <c r="C25" t="n">
-        <v>35.18877792358398</v>
+        <v>37.96709493116606</v>
       </c>
       <c r="D25" t="n">
-        <v>34.48940977503464</v>
+        <v>36.55877612240707</v>
       </c>
       <c r="E25" t="n">
-        <v>34.58521222922465</v>
+        <v>36.57793734517047</v>
       </c>
       <c r="F25" t="n">
-        <v>11133300</v>
+        <v>14205400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45867</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>35.04507446289062</v>
+        <v>36.50129318237305</v>
       </c>
       <c r="C26" t="n">
-        <v>36.34800465937124</v>
+        <v>37.68926343499903</v>
       </c>
       <c r="D26" t="n">
-        <v>35.04507446289062</v>
+        <v>36.36716827498278</v>
       </c>
       <c r="E26" t="n">
-        <v>35.59115649539564</v>
+        <v>37.29646749708626</v>
       </c>
       <c r="F26" t="n">
-        <v>14293400</v>
+        <v>7471100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45868</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>35.30374145507812</v>
+        <v>35.65821838378906</v>
       </c>
       <c r="C27" t="n">
-        <v>35.90730714696772</v>
+        <v>36.56835265389517</v>
       </c>
       <c r="D27" t="n">
-        <v>34.2498998447827</v>
+        <v>35.47618860606438</v>
       </c>
       <c r="E27" t="n">
-        <v>35.11213654748212</v>
+        <v>36.53003386535832</v>
       </c>
       <c r="F27" t="n">
-        <v>18990800</v>
+        <v>9567300</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45869</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>35.55282592773438</v>
+        <v>35.07381057739258</v>
       </c>
       <c r="C28" t="n">
-        <v>35.76359566567303</v>
+        <v>36.07017207707545</v>
       </c>
       <c r="D28" t="n">
-        <v>34.39359967832885</v>
+        <v>34.98758691579254</v>
       </c>
       <c r="E28" t="n">
-        <v>35.07380645396728</v>
+        <v>36.07017207707545</v>
       </c>
       <c r="F28" t="n">
-        <v>15042800</v>
+        <v>6654500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45870</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>35.61989593505859</v>
+        <v>35.08338928222656</v>
       </c>
       <c r="C29" t="n">
-        <v>35.75402083148994</v>
+        <v>35.33248148390988</v>
       </c>
       <c r="D29" t="n">
-        <v>34.81514290184119</v>
+        <v>34.73849463659057</v>
       </c>
       <c r="E29" t="n">
-        <v>35.70611960485436</v>
+        <v>35.08338928222656</v>
       </c>
       <c r="F29" t="n">
-        <v>16118400</v>
+        <v>7988800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>35.5145149230957</v>
+        <v>34.9588508605957</v>
       </c>
       <c r="C30" t="n">
-        <v>36.20430435681071</v>
+        <v>35.3324855515058</v>
       </c>
       <c r="D30" t="n">
-        <v>35.46661369122766</v>
+        <v>34.53731128756531</v>
       </c>
       <c r="E30" t="n">
-        <v>35.84024841628004</v>
+        <v>34.90136719482899</v>
       </c>
       <c r="F30" t="n">
-        <v>6629900</v>
+        <v>5821900</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>35.57199096679688</v>
+        <v>34.46067047119141</v>
       </c>
       <c r="C31" t="n">
-        <v>35.84024073144381</v>
+        <v>35.25584109011741</v>
       </c>
       <c r="D31" t="n">
-        <v>35.38038242577951</v>
+        <v>34.22116067621149</v>
       </c>
       <c r="E31" t="n">
-        <v>35.51450730810298</v>
+        <v>35.25584109011741</v>
       </c>
       <c r="F31" t="n">
-        <v>5735100</v>
+        <v>7183300</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45875</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>36.55877685546875</v>
+        <v>34.88220596313477</v>
       </c>
       <c r="C32" t="n">
-        <v>36.6162605249116</v>
+        <v>35.02591330019658</v>
       </c>
       <c r="D32" t="n">
-        <v>35.75402375641697</v>
+        <v>34.56605493807994</v>
       </c>
       <c r="E32" t="n">
-        <v>35.83066864900744</v>
+        <v>34.63311738747428</v>
       </c>
       <c r="F32" t="n">
-        <v>9789400</v>
+        <v>5425600</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45876</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>37.363525390625</v>
+        <v>34.1061897277832</v>
       </c>
       <c r="C33" t="n">
-        <v>37.96709105484666</v>
+        <v>34.61395292446204</v>
       </c>
       <c r="D33" t="n">
-        <v>36.55877238987252</v>
+        <v>33.88584117831577</v>
       </c>
       <c r="E33" t="n">
-        <v>36.57793361067963</v>
+        <v>34.48940682097903</v>
       </c>
       <c r="F33" t="n">
-        <v>14205400</v>
+        <v>5848800</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45877</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>36.50128936767578</v>
+        <v>34.55647659301758</v>
       </c>
       <c r="C34" t="n">
-        <v>37.68925949614871</v>
+        <v>34.55647659301758</v>
       </c>
       <c r="D34" t="n">
-        <v>36.36716447430271</v>
+        <v>33.77088467451971</v>
       </c>
       <c r="E34" t="n">
-        <v>37.29646359928648</v>
+        <v>34.04871694327939</v>
       </c>
       <c r="F34" t="n">
-        <v>7471100</v>
+        <v>7037900</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45880</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>35.6582145690918</v>
+        <v>34.4031867980957</v>
       </c>
       <c r="C35" t="n">
-        <v>36.56834874183222</v>
+        <v>34.76724270969122</v>
       </c>
       <c r="D35" t="n">
-        <v>35.47618481084056</v>
+        <v>34.31696312573438</v>
       </c>
       <c r="E35" t="n">
-        <v>36.5300299573947</v>
+        <v>34.31696312573438</v>
       </c>
       <c r="F35" t="n">
-        <v>9567300</v>
+        <v>4723200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45881</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>35.07381057739258</v>
+        <v>35.92646789550781</v>
       </c>
       <c r="C36" t="n">
-        <v>36.07017207707545</v>
+        <v>35.97436912177596</v>
       </c>
       <c r="D36" t="n">
-        <v>34.98758691579254</v>
+        <v>34.42234673198623</v>
       </c>
       <c r="E36" t="n">
-        <v>36.07017207707545</v>
+        <v>34.63311651312125</v>
       </c>
       <c r="F36" t="n">
-        <v>6654500</v>
+        <v>10637800</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45882</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>35.0833854675293</v>
+        <v>36.14682006835938</v>
       </c>
       <c r="C37" t="n">
-        <v>35.33247764212825</v>
+        <v>36.39591231722599</v>
       </c>
       <c r="D37" t="n">
-        <v>34.73849085939448</v>
+        <v>35.88814903513466</v>
       </c>
       <c r="E37" t="n">
-        <v>35.0833854675293</v>
+        <v>36.0605963906178</v>
       </c>
       <c r="F37" t="n">
-        <v>7988800</v>
+        <v>8394800</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45883</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>34.9588508605957</v>
+        <v>36.01269149780273</v>
       </c>
       <c r="C38" t="n">
-        <v>35.3324855515058</v>
+        <v>36.34800373568675</v>
       </c>
       <c r="D38" t="n">
-        <v>34.53731128756531</v>
+        <v>35.8019217170589</v>
       </c>
       <c r="E38" t="n">
-        <v>34.90136719482899</v>
+        <v>36.21387884053314</v>
       </c>
       <c r="F38" t="n">
-        <v>5821900</v>
+        <v>13465700</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>34.46067047119141</v>
+        <v>36.15639877319336</v>
       </c>
       <c r="C39" t="n">
-        <v>35.25584109011741</v>
+        <v>36.47254978917462</v>
       </c>
       <c r="D39" t="n">
-        <v>34.22116067621149</v>
+        <v>35.80192165984893</v>
       </c>
       <c r="E39" t="n">
-        <v>35.25584109011741</v>
+        <v>36.09891510909254</v>
       </c>
       <c r="F39" t="n">
-        <v>7183300</v>
+        <v>7509800</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>34.8822021484375</v>
+        <v>36.23303604125977</v>
       </c>
       <c r="C40" t="n">
-        <v>35.02590946978356</v>
+        <v>36.71205555915546</v>
       </c>
       <c r="D40" t="n">
-        <v>34.56605115795676</v>
+        <v>36.06058872244701</v>
       </c>
       <c r="E40" t="n">
-        <v>34.63311360001719</v>
+        <v>36.40548336007252</v>
       </c>
       <c r="F40" t="n">
-        <v>5425600</v>
+        <v>11601700</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45888</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>34.10619354248047</v>
+        <v>36.07975006103516</v>
       </c>
       <c r="C41" t="n">
-        <v>34.61395679595142</v>
+        <v>36.50128592251099</v>
       </c>
       <c r="D41" t="n">
-        <v>33.88584496836756</v>
+        <v>36.00310883832541</v>
       </c>
       <c r="E41" t="n">
-        <v>34.48941067853823</v>
+        <v>36.27135859975287</v>
       </c>
       <c r="F41" t="n">
-        <v>5848800</v>
+        <v>12724500</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45889</v>
+        <v>45901</v>
       </c>
       <c r="B42" t="n">
-        <v>34.55647659301758</v>
+        <v>36.22346115112305</v>
       </c>
       <c r="C42" t="n">
-        <v>34.55647659301758</v>
+        <v>36.39590848846515</v>
       </c>
       <c r="D42" t="n">
-        <v>33.77088467451971</v>
+        <v>35.92646770244959</v>
       </c>
       <c r="E42" t="n">
-        <v>34.04871694327939</v>
+        <v>36.33842482447469</v>
       </c>
       <c r="F42" t="n">
-        <v>7037900</v>
+        <v>4831500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45890</v>
+        <v>45902</v>
       </c>
       <c r="B43" t="n">
-        <v>34.4031867980957</v>
+        <v>36.09891510009766</v>
       </c>
       <c r="C43" t="n">
-        <v>34.76724270969122</v>
+        <v>36.4054873326337</v>
       </c>
       <c r="D43" t="n">
-        <v>34.31696312573438</v>
+        <v>35.89772775773887</v>
       </c>
       <c r="E43" t="n">
-        <v>34.31696312573438</v>
+        <v>35.9647902051918</v>
       </c>
       <c r="F43" t="n">
-        <v>4723200</v>
+        <v>7248500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45891</v>
+        <v>45903</v>
       </c>
       <c r="B44" t="n">
-        <v>35.92647171020508</v>
+        <v>36.26177978515625</v>
       </c>
       <c r="C44" t="n">
-        <v>35.97437294155941</v>
+        <v>36.27136222309527</v>
       </c>
       <c r="D44" t="n">
-        <v>34.42235038697487</v>
+        <v>35.84024388157091</v>
       </c>
       <c r="E44" t="n">
-        <v>34.63312019048957</v>
+        <v>36.1851385547904</v>
       </c>
       <c r="F44" t="n">
-        <v>10637800</v>
+        <v>8758100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45894</v>
+        <v>45904</v>
       </c>
       <c r="B45" t="n">
-        <v>36.14681625366211</v>
+        <v>35.68695449829102</v>
       </c>
       <c r="C45" t="n">
-        <v>36.39590847624117</v>
+        <v>36.35758256207059</v>
       </c>
       <c r="D45" t="n">
-        <v>35.88814524773584</v>
+        <v>35.68695449829102</v>
       </c>
       <c r="E45" t="n">
-        <v>36.06059258502002</v>
+        <v>36.14681280226386</v>
       </c>
       <c r="F45" t="n">
-        <v>8394800</v>
+        <v>8614300</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45895</v>
+        <v>45905</v>
       </c>
       <c r="B46" t="n">
-        <v>36.01269149780273</v>
+        <v>36.26177978515625</v>
       </c>
       <c r="C46" t="n">
-        <v>36.34800373568675</v>
+        <v>36.63541811756355</v>
       </c>
       <c r="D46" t="n">
-        <v>35.8019217170589</v>
+        <v>35.9743687756831</v>
       </c>
       <c r="E46" t="n">
-        <v>36.21387884053314</v>
+        <v>35.9743687756831</v>
       </c>
       <c r="F46" t="n">
-        <v>13465700</v>
+        <v>6112300</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45896</v>
+        <v>45908</v>
       </c>
       <c r="B47" t="n">
-        <v>36.15639877319336</v>
+        <v>35.86898422241211</v>
       </c>
       <c r="C47" t="n">
-        <v>36.47254978917462</v>
+        <v>36.40548745852001</v>
       </c>
       <c r="D47" t="n">
-        <v>35.80192165984893</v>
+        <v>35.61989565310123</v>
       </c>
       <c r="E47" t="n">
-        <v>36.09891510909254</v>
+        <v>36.27136256315035</v>
       </c>
       <c r="F47" t="n">
-        <v>7509800</v>
+        <v>6063500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="B48" t="n">
-        <v>36.23303604125977</v>
+        <v>35.42828369140625</v>
       </c>
       <c r="C48" t="n">
-        <v>36.71205555915546</v>
+        <v>36.05101053682936</v>
       </c>
       <c r="D48" t="n">
-        <v>36.06058872244701</v>
+        <v>35.4091224718178</v>
       </c>
       <c r="E48" t="n">
-        <v>36.40548336007252</v>
+        <v>35.69653345638657</v>
       </c>
       <c r="F48" t="n">
-        <v>11601700</v>
+        <v>5401000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45898</v>
+        <v>45910</v>
       </c>
       <c r="B49" t="n">
-        <v>36.07975387573242</v>
+        <v>35.7156982421875</v>
       </c>
       <c r="C49" t="n">
-        <v>36.50128978177707</v>
+        <v>35.97436925051638</v>
       </c>
       <c r="D49" t="n">
-        <v>36.00311264491943</v>
+        <v>35.40912600741905</v>
       </c>
       <c r="E49" t="n">
-        <v>36.27136243470883</v>
+        <v>35.44744845042244</v>
       </c>
       <c r="F49" t="n">
-        <v>12724500</v>
+        <v>6369400</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45901</v>
+        <v>45911</v>
       </c>
       <c r="B50" t="n">
-        <v>36.22346115112305</v>
+        <v>35.28458404541016</v>
       </c>
       <c r="C50" t="n">
-        <v>36.39590848846515</v>
+        <v>35.87856730179182</v>
       </c>
       <c r="D50" t="n">
-        <v>35.92646770244959</v>
+        <v>35.16961671478452</v>
       </c>
       <c r="E50" t="n">
-        <v>36.33842482447469</v>
+        <v>35.821083636479</v>
       </c>
       <c r="F50" t="n">
-        <v>4831500</v>
+        <v>6560300</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="B51" t="n">
-        <v>36.09891128540039</v>
+        <v>35.3995475769043</v>
       </c>
       <c r="C51" t="n">
-        <v>36.40548348553989</v>
+        <v>35.44744880382143</v>
       </c>
       <c r="D51" t="n">
-        <v>35.89772396430176</v>
+        <v>34.939689220167</v>
       </c>
       <c r="E51" t="n">
-        <v>35.96478640466797</v>
+        <v>35.09297533907943</v>
       </c>
       <c r="F51" t="n">
-        <v>7248500</v>
+        <v>4908900</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="B52" t="n">
-        <v>36.26177978515625</v>
+        <v>34.97800445556641</v>
       </c>
       <c r="C52" t="n">
-        <v>36.27136222309527</v>
+        <v>35.4761852050798</v>
       </c>
       <c r="D52" t="n">
-        <v>35.84024388157091</v>
+        <v>34.77681713017513</v>
       </c>
       <c r="E52" t="n">
-        <v>36.1851385547904</v>
+        <v>35.13129055890676</v>
       </c>
       <c r="F52" t="n">
-        <v>8758100</v>
+        <v>6287600</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45904</v>
+        <v>45916</v>
       </c>
       <c r="B53" t="n">
-        <v>35.68695831298828</v>
+        <v>35.22710037231445</v>
       </c>
       <c r="C53" t="n">
-        <v>36.35758644845352</v>
+        <v>35.36122527005203</v>
       </c>
       <c r="D53" t="n">
-        <v>35.68695831298828</v>
+        <v>34.91094569510785</v>
       </c>
       <c r="E53" t="n">
-        <v>36.14681666611691</v>
+        <v>35.18877792878104</v>
       </c>
       <c r="F53" t="n">
-        <v>8614300</v>
+        <v>6047700</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="B54" t="n">
-        <v>36.26177978515625</v>
+        <v>35.16961669921875</v>
       </c>
       <c r="C54" t="n">
-        <v>36.63541811756355</v>
+        <v>35.4282877110679</v>
       </c>
       <c r="D54" t="n">
-        <v>35.9743687756831</v>
+        <v>34.93010690913206</v>
       </c>
       <c r="E54" t="n">
-        <v>35.9743687756831</v>
+        <v>35.24626158626859</v>
       </c>
       <c r="F54" t="n">
-        <v>6112300</v>
+        <v>9531700</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="B55" t="n">
-        <v>35.86898422241211</v>
+        <v>35.18877792358398</v>
       </c>
       <c r="C55" t="n">
-        <v>36.40548745852001</v>
+        <v>35.39954770835726</v>
       </c>
       <c r="D55" t="n">
-        <v>35.61989565310123</v>
+        <v>34.88220568462069</v>
       </c>
       <c r="E55" t="n">
-        <v>36.27136256315035</v>
+        <v>35.26542281063949</v>
       </c>
       <c r="F55" t="n">
-        <v>6063500</v>
+        <v>7699800</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45909</v>
+        <v>45919</v>
       </c>
       <c r="B56" t="n">
-        <v>35.42828750610352</v>
+        <v>34.8247184753418</v>
       </c>
       <c r="C56" t="n">
-        <v>36.05101441857798</v>
+        <v>35.43786654549986</v>
       </c>
       <c r="D56" t="n">
-        <v>35.40912628445191</v>
+        <v>34.8247184753418</v>
       </c>
       <c r="E56" t="n">
-        <v>35.6965372999673</v>
+        <v>35.18877434254805</v>
       </c>
       <c r="F56" t="n">
-        <v>5401000</v>
+        <v>9696300</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45910</v>
+        <v>45922</v>
       </c>
       <c r="B57" t="n">
-        <v>35.71569442749023</v>
+        <v>35.55283355712891</v>
       </c>
       <c r="C57" t="n">
-        <v>35.97436540819115</v>
+        <v>35.67737967033109</v>
       </c>
       <c r="D57" t="n">
-        <v>35.40912222546594</v>
+        <v>34.55647196077012</v>
       </c>
       <c r="E57" t="n">
-        <v>35.44744466437621</v>
+        <v>34.79598174905083</v>
       </c>
       <c r="F57" t="n">
-        <v>6369400</v>
+        <v>17499300</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="B58" t="n">
-        <v>35.28458404541016</v>
+        <v>35.16003799438477</v>
       </c>
       <c r="C58" t="n">
-        <v>35.87856730179182</v>
+        <v>35.84024492264309</v>
       </c>
       <c r="D58" t="n">
-        <v>35.16961671478452</v>
+        <v>35.09297554538067</v>
       </c>
       <c r="E58" t="n">
-        <v>35.821083636479</v>
+        <v>35.55283390482134</v>
       </c>
       <c r="F58" t="n">
-        <v>6560300</v>
+        <v>6867600</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45912</v>
+        <v>45924</v>
       </c>
       <c r="B59" t="n">
-        <v>35.39954376220703</v>
+        <v>35.34206390380859</v>
       </c>
       <c r="C59" t="n">
-        <v>35.44744498396227</v>
+        <v>35.533672466063</v>
       </c>
       <c r="D59" t="n">
-        <v>34.93968545502462</v>
+        <v>35.06423167127117</v>
       </c>
       <c r="E59" t="n">
-        <v>35.09297155741876</v>
+        <v>35.1983602230898</v>
       </c>
       <c r="F59" t="n">
-        <v>4908900</v>
+        <v>4562300</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="B60" t="n">
-        <v>34.97800827026367</v>
+        <v>34.8247184753418</v>
       </c>
       <c r="C60" t="n">
-        <v>35.4761890741086</v>
+        <v>35.43786654549986</v>
       </c>
       <c r="D60" t="n">
-        <v>34.77682092293092</v>
+        <v>34.59479114683289</v>
       </c>
       <c r="E60" t="n">
-        <v>35.13129439032139</v>
+        <v>35.43786654549986</v>
       </c>
       <c r="F60" t="n">
-        <v>6287600</v>
+        <v>8075800</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45916</v>
+        <v>45926</v>
       </c>
       <c r="B61" t="n">
-        <v>35.22710037231445</v>
+        <v>34.79598236083984</v>
       </c>
       <c r="C61" t="n">
-        <v>35.36122527005203</v>
+        <v>35.06423215894926</v>
       </c>
       <c r="D61" t="n">
-        <v>34.91094569510785</v>
+        <v>34.69059746740274</v>
       </c>
       <c r="E61" t="n">
-        <v>35.18877792878104</v>
+        <v>34.95885092014156</v>
       </c>
       <c r="F61" t="n">
-        <v>6047700</v>
+        <v>4491900</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45917</v>
+        <v>45929</v>
       </c>
       <c r="B62" t="n">
-        <v>35.16961669921875</v>
+        <v>34.94995880126953</v>
       </c>
       <c r="C62" t="n">
-        <v>35.4282877110679</v>
+        <v>35.52653443752794</v>
       </c>
       <c r="D62" t="n">
-        <v>34.93010690913206</v>
+        <v>34.62323370711633</v>
       </c>
       <c r="E62" t="n">
-        <v>35.24626158626859</v>
+        <v>35.52653443752794</v>
       </c>
       <c r="F62" t="n">
-        <v>9531700</v>
+        <v>4873200</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="B63" t="n">
-        <v>35.18877792358398</v>
+        <v>35.16137313842773</v>
       </c>
       <c r="C63" t="n">
-        <v>35.39954770835726</v>
+        <v>35.35356503305353</v>
       </c>
       <c r="D63" t="n">
-        <v>34.88220568462069</v>
+        <v>34.83464801729051</v>
       </c>
       <c r="E63" t="n">
-        <v>35.26542281063949</v>
+        <v>35.17098108356905</v>
       </c>
       <c r="F63" t="n">
-        <v>7699800</v>
+        <v>7668000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="B64" t="n">
-        <v>34.8247184753418</v>
+        <v>34.39260864257812</v>
       </c>
       <c r="C64" t="n">
-        <v>35.43786654549986</v>
+        <v>34.94035315023399</v>
       </c>
       <c r="D64" t="n">
-        <v>34.8247184753418</v>
+        <v>34.13315013909555</v>
       </c>
       <c r="E64" t="n">
-        <v>35.18877434254805</v>
+        <v>34.87308653811873</v>
       </c>
       <c r="F64" t="n">
-        <v>9696300</v>
+        <v>11275700</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45922</v>
+        <v>45932</v>
       </c>
       <c r="B65" t="n">
-        <v>35.55282592773438</v>
+        <v>34.71933364868164</v>
       </c>
       <c r="C65" t="n">
-        <v>35.67737201420982</v>
+        <v>34.9307414293391</v>
       </c>
       <c r="D65" t="n">
-        <v>34.55646454518796</v>
+        <v>34.34456147786275</v>
       </c>
       <c r="E65" t="n">
-        <v>34.79597428207151</v>
+        <v>34.46948309096544</v>
       </c>
       <c r="F65" t="n">
-        <v>17499300</v>
+        <v>8501800</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="B66" t="n">
-        <v>35.1600341796875</v>
+        <v>34.97879028320312</v>
       </c>
       <c r="C66" t="n">
-        <v>35.84024103414659</v>
+        <v>35.69950708574916</v>
       </c>
       <c r="D66" t="n">
-        <v>35.09297173795936</v>
+        <v>34.77698679251627</v>
       </c>
       <c r="E66" t="n">
-        <v>35.55283004750758</v>
+        <v>34.78659840270647</v>
       </c>
       <c r="F66" t="n">
-        <v>6867600</v>
+        <v>7971200</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45924</v>
+        <v>45936</v>
       </c>
       <c r="B67" t="n">
-        <v>35.34206390380859</v>
+        <v>34.28689575195312</v>
       </c>
       <c r="C67" t="n">
-        <v>35.533672466063</v>
+        <v>35.14214564071928</v>
       </c>
       <c r="D67" t="n">
-        <v>35.06423167127117</v>
+        <v>34.15236255584447</v>
       </c>
       <c r="E67" t="n">
-        <v>35.1983602230898</v>
+        <v>34.98839289291586</v>
       </c>
       <c r="F67" t="n">
-        <v>4562300</v>
+        <v>10721600</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="B68" t="n">
-        <v>34.8247184753418</v>
+        <v>34.33494567871094</v>
       </c>
       <c r="C68" t="n">
-        <v>35.43786654549986</v>
+        <v>34.89230172735222</v>
       </c>
       <c r="D68" t="n">
-        <v>34.59479114683289</v>
+        <v>34.21002041509221</v>
       </c>
       <c r="E68" t="n">
-        <v>35.43786654549986</v>
+        <v>34.27728701878961</v>
       </c>
       <c r="F68" t="n">
-        <v>8075800</v>
+        <v>5190500</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="B69" t="n">
-        <v>34.79598236083984</v>
+        <v>34.11392593383789</v>
       </c>
       <c r="C69" t="n">
-        <v>35.06423215894926</v>
+        <v>34.60401170756086</v>
       </c>
       <c r="D69" t="n">
-        <v>34.69059746740274</v>
+        <v>34.02743977779797</v>
       </c>
       <c r="E69" t="n">
-        <v>34.95885092014156</v>
+        <v>34.48869805475927</v>
       </c>
       <c r="F69" t="n">
-        <v>4491900</v>
+        <v>6387700</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45929</v>
+        <v>45939</v>
       </c>
       <c r="B70" t="n">
-        <v>34.9499626159668</v>
+        <v>35.74755096435547</v>
       </c>
       <c r="C70" t="n">
-        <v>35.52653831515694</v>
+        <v>35.891692112609</v>
       </c>
       <c r="D70" t="n">
-        <v>34.62323748615239</v>
+        <v>34.21963133203669</v>
       </c>
       <c r="E70" t="n">
-        <v>35.52653831515694</v>
+        <v>34.21963133203669</v>
       </c>
       <c r="F70" t="n">
-        <v>4873200</v>
+        <v>14768200</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="B71" t="n">
-        <v>35.16136932373047</v>
+        <v>35.25746917724609</v>
       </c>
       <c r="C71" t="n">
-        <v>35.35356119750516</v>
+        <v>36.2088170914037</v>
       </c>
       <c r="D71" t="n">
-        <v>34.83464423804003</v>
+        <v>35.25746917724609</v>
       </c>
       <c r="E71" t="n">
-        <v>35.17097726782941</v>
+        <v>35.79560577841921</v>
       </c>
       <c r="F71" t="n">
-        <v>7668000</v>
+        <v>10273600</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="B72" t="n">
-        <v>34.39260864257812</v>
+        <v>36.36256408691406</v>
       </c>
       <c r="C72" t="n">
-        <v>34.94035315023399</v>
+        <v>36.47787774530268</v>
       </c>
       <c r="D72" t="n">
-        <v>34.13315013909555</v>
+        <v>35.34394971817508</v>
       </c>
       <c r="E72" t="n">
-        <v>34.87308653811873</v>
+        <v>35.35356132806461</v>
       </c>
       <c r="F72" t="n">
-        <v>11275700</v>
+        <v>11420200</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="B73" t="n">
-        <v>34.71933364868164</v>
+        <v>35.87247467041016</v>
       </c>
       <c r="C73" t="n">
-        <v>34.9307414293391</v>
+        <v>36.6124072640304</v>
       </c>
       <c r="D73" t="n">
-        <v>34.34456147786275</v>
+        <v>35.85325511832519</v>
       </c>
       <c r="E73" t="n">
-        <v>34.46948309096544</v>
+        <v>36.20880766751026</v>
       </c>
       <c r="F73" t="n">
-        <v>8501800</v>
+        <v>10186200</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45933</v>
+        <v>45945</v>
       </c>
       <c r="B74" t="n">
-        <v>34.97879028320312</v>
+        <v>35.95896148681641</v>
       </c>
       <c r="C74" t="n">
-        <v>35.69950708574916</v>
+        <v>36.37217274202078</v>
       </c>
       <c r="D74" t="n">
-        <v>34.77698679251627</v>
+        <v>35.82442827177408</v>
       </c>
       <c r="E74" t="n">
-        <v>34.78659840270647</v>
+        <v>35.9205260437723</v>
       </c>
       <c r="F74" t="n">
-        <v>7971200</v>
+        <v>7314800</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="B75" t="n">
-        <v>34.28689956665039</v>
+        <v>36.92953109741211</v>
       </c>
       <c r="C75" t="n">
-        <v>35.14214955057008</v>
+        <v>37.07367593141197</v>
       </c>
       <c r="D75" t="n">
-        <v>34.15236635557382</v>
+        <v>35.84365003434456</v>
       </c>
       <c r="E75" t="n">
-        <v>34.98839678566042</v>
+        <v>36.12232809167475</v>
       </c>
       <c r="F75" t="n">
-        <v>10721600</v>
+        <v>10795000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c r="B76" t="n">
-        <v>34.3349494934082</v>
+        <v>38.58237838745117</v>
       </c>
       <c r="C76" t="n">
-        <v>34.89230560397312</v>
+        <v>39.07246425222196</v>
       </c>
       <c r="D76" t="n">
-        <v>34.21002421590997</v>
+        <v>36.73734127108127</v>
       </c>
       <c r="E76" t="n">
-        <v>34.27729082708085</v>
+        <v>36.81421949773467</v>
       </c>
       <c r="F76" t="n">
-        <v>5190500</v>
+        <v>28853800</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45938</v>
+        <v>45950</v>
       </c>
       <c r="B77" t="n">
-        <v>34.11392974853516</v>
+        <v>37.99618911743164</v>
       </c>
       <c r="C77" t="n">
-        <v>34.60401557706064</v>
+        <v>38.63041973045873</v>
       </c>
       <c r="D77" t="n">
-        <v>34.02744358282415</v>
+        <v>37.99618911743164</v>
       </c>
       <c r="E77" t="n">
-        <v>34.48870191136441</v>
+        <v>38.52471401732837</v>
       </c>
       <c r="F77" t="n">
-        <v>6387700</v>
+        <v>12463500</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="B78" t="n">
-        <v>35.74755859375</v>
+        <v>38.12111282348633</v>
       </c>
       <c r="C78" t="n">
-        <v>35.89169977276675</v>
+        <v>38.41901042550623</v>
       </c>
       <c r="D78" t="n">
-        <v>34.21963863533611</v>
+        <v>37.84243844210253</v>
       </c>
       <c r="E78" t="n">
-        <v>34.21963863533611</v>
+        <v>38.09228532404273</v>
       </c>
       <c r="F78" t="n">
-        <v>14768200</v>
+        <v>10407600</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45940</v>
+        <v>45952</v>
       </c>
       <c r="B79" t="n">
-        <v>35.25746536254883</v>
+        <v>38.45744705200195</v>
       </c>
       <c r="C79" t="n">
-        <v>36.20881317377494</v>
+        <v>39.18777176153862</v>
       </c>
       <c r="D79" t="n">
-        <v>35.25746536254883</v>
+        <v>37.16976628417662</v>
       </c>
       <c r="E79" t="n">
-        <v>35.79560190549802</v>
+        <v>37.66946368154593</v>
       </c>
       <c r="F79" t="n">
-        <v>10273600</v>
+        <v>16229100</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45943</v>
+        <v>45953</v>
       </c>
       <c r="B80" t="n">
-        <v>36.36256408691406</v>
+        <v>39.82200622558594</v>
       </c>
       <c r="C80" t="n">
-        <v>36.47787774530268</v>
+        <v>40.04302561521772</v>
       </c>
       <c r="D80" t="n">
-        <v>35.34394971817508</v>
+        <v>38.62081149992058</v>
       </c>
       <c r="E80" t="n">
-        <v>35.35356132806461</v>
+        <v>38.89948955605624</v>
       </c>
       <c r="F80" t="n">
-        <v>11420200</v>
+        <v>15783500</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="B81" t="n">
-        <v>35.87247848510742</v>
+        <v>39.75473785400391</v>
       </c>
       <c r="C81" t="n">
-        <v>36.61241115741247</v>
+        <v>40.15834117015008</v>
       </c>
       <c r="D81" t="n">
-        <v>35.85325893097863</v>
+        <v>39.39918525736113</v>
       </c>
       <c r="E81" t="n">
-        <v>36.20881151797335</v>
+        <v>39.83161607260516</v>
       </c>
       <c r="F81" t="n">
-        <v>10186200</v>
+        <v>10015800</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45945</v>
+        <v>45957</v>
       </c>
       <c r="B82" t="n">
-        <v>35.95896148681641</v>
+        <v>40.04302215576172</v>
       </c>
       <c r="C82" t="n">
-        <v>36.37217274202078</v>
+        <v>40.69647232333027</v>
       </c>
       <c r="D82" t="n">
-        <v>35.82442827177408</v>
+        <v>39.87966144674711</v>
       </c>
       <c r="E82" t="n">
-        <v>35.9205260437723</v>
+        <v>40.36013929550311</v>
       </c>
       <c r="F82" t="n">
-        <v>7314800</v>
+        <v>11591400</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45946</v>
+        <v>45958</v>
       </c>
       <c r="B83" t="n">
-        <v>36.92953109741211</v>
+        <v>40.66764831542969</v>
       </c>
       <c r="C83" t="n">
-        <v>37.07367593141197</v>
+        <v>41.18656531639937</v>
       </c>
       <c r="D83" t="n">
-        <v>35.84365003434456</v>
+        <v>40.04302559214151</v>
       </c>
       <c r="E83" t="n">
-        <v>36.12232809167475</v>
+        <v>40.11990381410237</v>
       </c>
       <c r="F83" t="n">
-        <v>10795000</v>
+        <v>9574200</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45947</v>
+        <v>45959</v>
       </c>
       <c r="B84" t="n">
-        <v>38.58237838745117</v>
+        <v>40.4081916809082</v>
       </c>
       <c r="C84" t="n">
-        <v>39.07246425222196</v>
+        <v>41.54211984690563</v>
       </c>
       <c r="D84" t="n">
-        <v>36.73734127108127</v>
+        <v>40.34092506646391</v>
       </c>
       <c r="E84" t="n">
-        <v>36.81421949773467</v>
+        <v>40.77335592057404</v>
       </c>
       <c r="F84" t="n">
-        <v>28853800</v>
+        <v>12072900</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45950</v>
+        <v>45960</v>
       </c>
       <c r="B85" t="n">
-        <v>37.99619293212891</v>
+        <v>39.83161544799805</v>
       </c>
       <c r="C85" t="n">
-        <v>38.63042360883075</v>
+        <v>40.43701857984625</v>
       </c>
       <c r="D85" t="n">
-        <v>37.99619293212891</v>
+        <v>39.6970822333107</v>
       </c>
       <c r="E85" t="n">
-        <v>38.52471788508787</v>
+        <v>40.28326214505481</v>
       </c>
       <c r="F85" t="n">
-        <v>12463500</v>
+        <v>11980500</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45951</v>
+        <v>45961</v>
       </c>
       <c r="B86" t="n">
-        <v>38.12111282348633</v>
+        <v>40.45623397827148</v>
       </c>
       <c r="C86" t="n">
-        <v>38.41901042550623</v>
+        <v>40.51389264061968</v>
       </c>
       <c r="D86" t="n">
-        <v>37.84243844210253</v>
+        <v>39.82200335546182</v>
       </c>
       <c r="E86" t="n">
-        <v>38.09228532404273</v>
+        <v>40.08146183739602</v>
       </c>
       <c r="F86" t="n">
-        <v>10407600</v>
+        <v>12528200</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="B87" t="n">
-        <v>38.45744705200195</v>
+        <v>41.12890625</v>
       </c>
       <c r="C87" t="n">
-        <v>39.18777176153862</v>
+        <v>41.22500402651664</v>
       </c>
       <c r="D87" t="n">
-        <v>37.16976628417662</v>
+        <v>40.34092281134024</v>
       </c>
       <c r="E87" t="n">
-        <v>37.66946368154593</v>
+        <v>40.73491453067012</v>
       </c>
       <c r="F87" t="n">
-        <v>16229100</v>
+        <v>8375200</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45953</v>
+        <v>45965</v>
       </c>
       <c r="B88" t="n">
-        <v>39.82200622558594</v>
+        <v>41.08085632324219</v>
       </c>
       <c r="C88" t="n">
-        <v>40.04302561521772</v>
+        <v>41.50367551309612</v>
       </c>
       <c r="D88" t="n">
-        <v>38.62081149992058</v>
+        <v>41.06163676928222</v>
       </c>
       <c r="E88" t="n">
-        <v>38.89948955605624</v>
+        <v>41.12890337526455</v>
       </c>
       <c r="F88" t="n">
-        <v>15783500</v>
+        <v>7341200</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45954</v>
+        <v>45966</v>
       </c>
       <c r="B89" t="n">
-        <v>39.75473785400391</v>
+        <v>41.81118392944336</v>
       </c>
       <c r="C89" t="n">
-        <v>40.15834117015008</v>
+        <v>41.89767009535222</v>
       </c>
       <c r="D89" t="n">
-        <v>39.39918525736113</v>
+        <v>40.77335360429241</v>
       </c>
       <c r="E89" t="n">
-        <v>39.83161607260516</v>
+        <v>41.08085915735604</v>
       </c>
       <c r="F89" t="n">
-        <v>10015800</v>
+        <v>6623200</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45957</v>
+        <v>45967</v>
       </c>
       <c r="B90" t="n">
-        <v>40.04302215576172</v>
+        <v>42.19557189941406</v>
       </c>
       <c r="C90" t="n">
-        <v>40.69647232333027</v>
+        <v>42.40698336282551</v>
       </c>
       <c r="D90" t="n">
-        <v>39.87966144674711</v>
+        <v>41.63821940372351</v>
       </c>
       <c r="E90" t="n">
-        <v>40.36013929550311</v>
+        <v>41.80158014126456</v>
       </c>
       <c r="F90" t="n">
-        <v>11591400</v>
+        <v>11139300</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="B91" t="n">
-        <v>40.66764831542969</v>
+        <v>43.24300765991211</v>
       </c>
       <c r="C91" t="n">
-        <v>41.18656531639937</v>
+        <v>43.35832132059376</v>
       </c>
       <c r="D91" t="n">
-        <v>40.04302559214151</v>
+        <v>41.99376594955457</v>
       </c>
       <c r="E91" t="n">
-        <v>40.11990381410237</v>
+        <v>42.18595782786078</v>
       </c>
       <c r="F91" t="n">
-        <v>9574200</v>
+        <v>12825500</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45959</v>
+        <v>45971</v>
       </c>
       <c r="B92" t="n">
-        <v>40.40818786621094</v>
+        <v>43.59856414794922</v>
       </c>
       <c r="C92" t="n">
-        <v>41.54211592516094</v>
+        <v>43.61778370407279</v>
       </c>
       <c r="D92" t="n">
-        <v>40.34092125811689</v>
+        <v>43.20457241180474</v>
       </c>
       <c r="E92" t="n">
-        <v>40.77335207140379</v>
+        <v>43.43520341953211</v>
       </c>
       <c r="F92" t="n">
-        <v>12072900</v>
+        <v>10066300</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45960</v>
+        <v>45972</v>
       </c>
       <c r="B93" t="n">
-        <v>39.83161544799805</v>
+        <v>44.23279190063477</v>
       </c>
       <c r="C93" t="n">
-        <v>40.43701857984625</v>
+        <v>44.81897549334597</v>
       </c>
       <c r="D93" t="n">
-        <v>39.6970822333107</v>
+        <v>43.72348652731433</v>
       </c>
       <c r="E93" t="n">
-        <v>40.28326214505481</v>
+        <v>43.97333340882381</v>
       </c>
       <c r="F93" t="n">
-        <v>11980500</v>
+        <v>10291400</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="B94" t="n">
-        <v>40.45623779296875</v>
+        <v>43.13730239868164</v>
       </c>
       <c r="C94" t="n">
-        <v>40.5138964607537</v>
+        <v>44.39615573240153</v>
       </c>
       <c r="D94" t="n">
-        <v>39.82200711035625</v>
+        <v>42.97394168313868</v>
       </c>
       <c r="E94" t="n">
-        <v>40.08146561675529</v>
+        <v>44.1559167984229</v>
       </c>
       <c r="F94" t="n">
-        <v>12528200</v>
+        <v>10226300</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45964</v>
+        <v>45974</v>
       </c>
       <c r="B95" t="n">
-        <v>41.12890625</v>
+        <v>43.07003402709961</v>
       </c>
       <c r="C95" t="n">
-        <v>41.22500402651664</v>
+        <v>43.36793161270877</v>
       </c>
       <c r="D95" t="n">
-        <v>40.34092281134024</v>
+        <v>42.68565028216876</v>
       </c>
       <c r="E95" t="n">
-        <v>40.73491453067012</v>
+        <v>43.05081447327756</v>
       </c>
       <c r="F95" t="n">
-        <v>8375200</v>
+        <v>10736800</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="B96" t="n">
-        <v>41.08085632324219</v>
+        <v>42.70487213134766</v>
       </c>
       <c r="C96" t="n">
-        <v>41.50367551309612</v>
+        <v>43.20456956031413</v>
       </c>
       <c r="D96" t="n">
-        <v>41.06163676928222</v>
+        <v>42.48385274914705</v>
       </c>
       <c r="E96" t="n">
-        <v>41.12890337526455</v>
+        <v>42.89706401414326</v>
       </c>
       <c r="F96" t="n">
-        <v>7341200</v>
+        <v>6639800</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="B97" t="n">
-        <v>41.81118392944336</v>
+        <v>42.25322341918945</v>
       </c>
       <c r="C97" t="n">
-        <v>41.89767009535222</v>
+        <v>42.77213671265429</v>
       </c>
       <c r="D97" t="n">
-        <v>40.77335360429241</v>
+        <v>41.97454538563559</v>
       </c>
       <c r="E97" t="n">
-        <v>41.08085915735604</v>
+        <v>42.57033689487601</v>
       </c>
       <c r="F97" t="n">
-        <v>6623200</v>
+        <v>9531800</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="B98" t="n">
-        <v>42.1955680847168</v>
+        <v>41.74391555786133</v>
       </c>
       <c r="C98" t="n">
-        <v>42.40697952901555</v>
+        <v>42.21478547811385</v>
       </c>
       <c r="D98" t="n">
-        <v>41.63821563941378</v>
+        <v>41.74391555786133</v>
       </c>
       <c r="E98" t="n">
-        <v>41.80157636218618</v>
+        <v>42.11869137149343</v>
       </c>
       <c r="F98" t="n">
-        <v>11139300</v>
+        <v>7190100</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="B99" t="n">
-        <v>43.24300765991211</v>
+        <v>41.94572067260742</v>
       </c>
       <c r="C99" t="n">
-        <v>43.35832132059376</v>
+        <v>42.17634800373663</v>
       </c>
       <c r="D99" t="n">
-        <v>41.99376594955457</v>
+        <v>41.51328984454599</v>
       </c>
       <c r="E99" t="n">
-        <v>42.18595782786078</v>
+        <v>41.70548173099055</v>
       </c>
       <c r="F99" t="n">
-        <v>12825500</v>
+        <v>7656600</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>43.59856033325195</v>
+        <v>41.53250885009766</v>
       </c>
       <c r="C100" t="n">
-        <v>43.61777988769389</v>
+        <v>42.14751994597653</v>
       </c>
       <c r="D100" t="n">
-        <v>43.20456863158016</v>
+        <v>41.02319980789679</v>
       </c>
       <c r="E100" t="n">
-        <v>43.43519961912825</v>
+        <v>41.76313617817459</v>
       </c>
       <c r="F100" t="n">
-        <v>10066300</v>
+        <v>9992100</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>44.23279190063477</v>
+        <v>41.50367736816406</v>
       </c>
       <c r="C101" t="n">
-        <v>44.81897549334597</v>
+        <v>41.71508880541792</v>
       </c>
       <c r="D101" t="n">
-        <v>43.72348652731433</v>
+        <v>41.33070504054822</v>
       </c>
       <c r="E101" t="n">
-        <v>43.97333340882381</v>
+        <v>41.71508880541792</v>
       </c>
       <c r="F101" t="n">
-        <v>10291400</v>
+        <v>12391300</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>43.13730239868164</v>
+        <v>41.28265762329102</v>
       </c>
       <c r="C102" t="n">
-        <v>44.39615573240153</v>
+        <v>41.7919666571272</v>
       </c>
       <c r="D102" t="n">
-        <v>42.97394168313868</v>
+        <v>41.10007735274912</v>
       </c>
       <c r="E102" t="n">
-        <v>44.1559167984229</v>
+        <v>41.73430799317729</v>
       </c>
       <c r="F102" t="n">
-        <v>10226300</v>
+        <v>4409100</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45974</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>43.07003784179688</v>
+        <v>42.66643524169922</v>
       </c>
       <c r="C103" t="n">
-        <v>43.36793545379072</v>
+        <v>42.90667417061474</v>
       </c>
       <c r="D103" t="n">
-        <v>42.68565406282129</v>
+        <v>41.43640943293823</v>
       </c>
       <c r="E103" t="n">
-        <v>43.05081828627256</v>
+        <v>41.43640943293823</v>
       </c>
       <c r="F103" t="n">
-        <v>10736800</v>
+        <v>8639200</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45975</v>
+        <v>45988</v>
       </c>
       <c r="B104" t="n">
-        <v>42.70487594604492</v>
+        <v>42.33010101318359</v>
       </c>
       <c r="C104" t="n">
-        <v>43.20457341964785</v>
+        <v>42.887457120371</v>
       </c>
       <c r="D104" t="n">
-        <v>42.48385654410132</v>
+        <v>42.29166190253163</v>
       </c>
       <c r="E104" t="n">
-        <v>42.89706784600845</v>
+        <v>42.83941006493372</v>
       </c>
       <c r="F104" t="n">
-        <v>6639800</v>
+        <v>3006400</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45978</v>
+        <v>45989</v>
       </c>
       <c r="B105" t="n">
-        <v>42.25322723388672</v>
+        <v>42.52229309082031</v>
       </c>
       <c r="C105" t="n">
-        <v>42.77214057419998</v>
+        <v>42.65682631294838</v>
       </c>
       <c r="D105" t="n">
-        <v>41.9745491751733</v>
+        <v>41.77274875853232</v>
       </c>
       <c r="E105" t="n">
-        <v>42.57034073820286</v>
+        <v>42.33010120245649</v>
       </c>
       <c r="F105" t="n">
-        <v>9531800</v>
+        <v>7531800</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45979</v>
+        <v>45992</v>
       </c>
       <c r="B106" t="n">
-        <v>41.74391555786133</v>
+        <v>43.41598129272461</v>
       </c>
       <c r="C106" t="n">
-        <v>42.21478547811385</v>
+        <v>43.65622023141133</v>
       </c>
       <c r="D106" t="n">
-        <v>41.74391555786133</v>
+        <v>42.28205320886286</v>
       </c>
       <c r="E106" t="n">
-        <v>42.11869137149343</v>
+        <v>42.93550341535116</v>
       </c>
       <c r="F106" t="n">
-        <v>7190100</v>
+        <v>17188500</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45980</v>
+        <v>45993</v>
       </c>
       <c r="B107" t="n">
-        <v>41.94572067260742</v>
+        <v>43.82919311523438</v>
       </c>
       <c r="C107" t="n">
-        <v>42.17634800373663</v>
+        <v>44.14630661212153</v>
       </c>
       <c r="D107" t="n">
-        <v>41.51328984454599</v>
+        <v>43.12769584528154</v>
       </c>
       <c r="E107" t="n">
-        <v>41.70548173099055</v>
+        <v>43.43520139743195</v>
       </c>
       <c r="F107" t="n">
-        <v>7656600</v>
+        <v>5818500</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="B108" t="n">
-        <v>41.53250503540039</v>
+        <v>43.29105758666992</v>
       </c>
       <c r="C108" t="n">
-        <v>42.14751607479143</v>
+        <v>44.02138603956097</v>
       </c>
       <c r="D108" t="n">
-        <v>41.02319603997879</v>
+        <v>43.29105758666992</v>
       </c>
       <c r="E108" t="n">
-        <v>41.76313234229455</v>
+        <v>44.0117744288423</v>
       </c>
       <c r="F108" t="n">
-        <v>9992100</v>
+        <v>10377300</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B109" t="n">
-        <v>41.50367736816406</v>
+        <v>44.16761016845703</v>
       </c>
       <c r="C109" t="n">
-        <v>41.71508880541792</v>
+        <v>44.16761016845703</v>
       </c>
       <c r="D109" t="n">
-        <v>41.33070504054822</v>
+        <v>43.34250244870398</v>
       </c>
       <c r="E109" t="n">
-        <v>41.71508880541792</v>
+        <v>43.56576684695492</v>
       </c>
       <c r="F109" t="n">
-        <v>12391300</v>
+        <v>7415000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="B110" t="n">
-        <v>41.28265762329102</v>
+        <v>45.33246612548828</v>
       </c>
       <c r="C110" t="n">
-        <v>41.7919666571272</v>
+        <v>45.51690094708275</v>
       </c>
       <c r="D110" t="n">
-        <v>41.10007735274912</v>
+        <v>44.16760546065328</v>
       </c>
       <c r="E110" t="n">
-        <v>41.73430799317729</v>
+        <v>44.16760546065328</v>
       </c>
       <c r="F110" t="n">
-        <v>4409100</v>
+        <v>15748300</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45987</v>
+        <v>45999</v>
       </c>
       <c r="B111" t="n">
-        <v>42.66643524169922</v>
+        <v>46.37113571166992</v>
       </c>
       <c r="C111" t="n">
-        <v>42.90667417061474</v>
+        <v>46.45850035997915</v>
       </c>
       <c r="D111" t="n">
-        <v>41.43640943293823</v>
+        <v>45.04125491228746</v>
       </c>
       <c r="E111" t="n">
-        <v>41.43640943293823</v>
+        <v>45.04125491228746</v>
       </c>
       <c r="F111" t="n">
-        <v>8639200</v>
+        <v>10859600</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45988</v>
+        <v>46000</v>
       </c>
       <c r="B112" t="n">
-        <v>42.33009719848633</v>
+        <v>46.26435852050781</v>
       </c>
       <c r="C112" t="n">
-        <v>42.887453255446</v>
+        <v>46.40996750905383</v>
       </c>
       <c r="D112" t="n">
-        <v>42.29165809129842</v>
+        <v>45.43925079338813</v>
       </c>
       <c r="E112" t="n">
-        <v>42.83940620433863</v>
+        <v>46.10904399412092</v>
       </c>
       <c r="F112" t="n">
-        <v>3006400</v>
+        <v>8650500</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="B113" t="n">
-        <v>42.52229309082031</v>
+        <v>47.05064010620117</v>
       </c>
       <c r="C113" t="n">
-        <v>42.65682631294838</v>
+        <v>47.14771029597932</v>
       </c>
       <c r="D113" t="n">
-        <v>41.77274875853232</v>
+        <v>46.10904371279352</v>
       </c>
       <c r="E113" t="n">
-        <v>42.33010120245649</v>
+        <v>46.3031877953402</v>
       </c>
       <c r="F113" t="n">
-        <v>7531800</v>
+        <v>4290600</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="B114" t="n">
-        <v>43.41598129272461</v>
+        <v>47.12829208374023</v>
       </c>
       <c r="C114" t="n">
-        <v>43.65622023141133</v>
+        <v>47.35155646635563</v>
       </c>
       <c r="D114" t="n">
-        <v>42.28205320886286</v>
+        <v>46.70117809564863</v>
       </c>
       <c r="E114" t="n">
-        <v>42.93550341535116</v>
+        <v>47.16712163801859</v>
       </c>
       <c r="F114" t="n">
-        <v>17188500</v>
+        <v>5154200</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="B115" t="n">
-        <v>43.82919692993164</v>
+        <v>48.06989288330078</v>
       </c>
       <c r="C115" t="n">
-        <v>44.14631045441894</v>
+        <v>48.06989288330078</v>
       </c>
       <c r="D115" t="n">
-        <v>43.12769959892361</v>
+        <v>46.5749882313365</v>
       </c>
       <c r="E115" t="n">
-        <v>43.43520517783794</v>
+        <v>47.27390546144768</v>
       </c>
       <c r="F115" t="n">
-        <v>5818500</v>
+        <v>9931700</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="B116" t="n">
-        <v>43.29105758666992</v>
+        <v>48.2252082824707</v>
       </c>
       <c r="C116" t="n">
-        <v>44.02138603956097</v>
+        <v>48.53583734524101</v>
       </c>
       <c r="D116" t="n">
-        <v>43.29105758666992</v>
+        <v>47.62336493622706</v>
       </c>
       <c r="E116" t="n">
-        <v>44.0117744288423</v>
+        <v>48.11842884783269</v>
       </c>
       <c r="F116" t="n">
-        <v>10377300</v>
+        <v>12049800</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="B117" t="n">
-        <v>44.16760635375977</v>
+        <v>48.47758865356445</v>
       </c>
       <c r="C117" t="n">
-        <v>44.16760635375977</v>
+        <v>48.63290317100076</v>
       </c>
       <c r="D117" t="n">
-        <v>43.34249870527017</v>
+        <v>47.61365141888809</v>
       </c>
       <c r="E117" t="n">
-        <v>43.56576308423806</v>
+        <v>47.84662504653765</v>
       </c>
       <c r="F117" t="n">
-        <v>7415000</v>
+        <v>10274800</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="B118" t="n">
-        <v>45.33246994018555</v>
+        <v>48.3416862487793</v>
       </c>
       <c r="C118" t="n">
-        <v>45.51690477730008</v>
+        <v>48.73967990920678</v>
       </c>
       <c r="D118" t="n">
-        <v>44.16760917732828</v>
+        <v>47.86603718540961</v>
       </c>
       <c r="E118" t="n">
-        <v>44.16760917732828</v>
+        <v>48.53583031061977</v>
       </c>
       <c r="F118" t="n">
-        <v>15748300</v>
+        <v>10202400</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="B119" t="n">
-        <v>46.37113571166992</v>
+        <v>48.53583145141602</v>
       </c>
       <c r="C119" t="n">
-        <v>46.45850035997915</v>
+        <v>49.17650427845511</v>
       </c>
       <c r="D119" t="n">
-        <v>45.04125491228746</v>
+        <v>48.11842300469463</v>
       </c>
       <c r="E119" t="n">
-        <v>45.04125491228746</v>
+        <v>48.18637287248741</v>
       </c>
       <c r="F119" t="n">
-        <v>10859600</v>
+        <v>5144100</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="B120" t="n">
-        <v>46.26435852050781</v>
+        <v>48.26403427124023</v>
       </c>
       <c r="C120" t="n">
-        <v>46.40996750905383</v>
+        <v>49.23475094634649</v>
       </c>
       <c r="D120" t="n">
-        <v>45.43925079338813</v>
+        <v>47.85633134214068</v>
       </c>
       <c r="E120" t="n">
-        <v>46.10904399412092</v>
+        <v>48.53583375531311</v>
       </c>
       <c r="F120" t="n">
-        <v>8650500</v>
+        <v>12839100</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="B121" t="n">
-        <v>47.05063629150391</v>
+        <v>47.44621276855469</v>
       </c>
       <c r="C121" t="n">
-        <v>47.14770647341195</v>
+        <v>48.63087345294175</v>
       </c>
       <c r="D121" t="n">
-        <v>46.10903997443751</v>
+        <v>46.96836634634178</v>
       </c>
       <c r="E121" t="n">
-        <v>46.30318404124369</v>
+        <v>48.48154858214222</v>
       </c>
       <c r="F121" t="n">
-        <v>4290600</v>
+        <v>6391700</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="B122" t="n">
-        <v>47.1282958984375</v>
+        <v>48.06343078613281</v>
       </c>
       <c r="C122" t="n">
-        <v>47.35156029912455</v>
+        <v>48.06343078613281</v>
       </c>
       <c r="D122" t="n">
-        <v>46.70118187577408</v>
+        <v>47.50594519005993</v>
       </c>
       <c r="E122" t="n">
-        <v>47.16712545585884</v>
+        <v>47.59554163194105</v>
       </c>
       <c r="F122" t="n">
-        <v>5154200</v>
+        <v>4886100</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46003</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>48.06988906860352</v>
+        <v>48.53132247924805</v>
       </c>
       <c r="C123" t="n">
-        <v>48.06988906860352</v>
+        <v>48.53132247924805</v>
       </c>
       <c r="D123" t="n">
-        <v>46.57498453527084</v>
+        <v>47.76477600694246</v>
       </c>
       <c r="E123" t="n">
-        <v>47.27390170991784</v>
+        <v>47.80459749065369</v>
       </c>
       <c r="F123" t="n">
-        <v>9931700</v>
+        <v>1829300</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>48.22520065307617</v>
+        <v>48.49150085449219</v>
       </c>
       <c r="C124" t="n">
-        <v>48.53582966670388</v>
+        <v>48.83993313957347</v>
       </c>
       <c r="D124" t="n">
-        <v>47.62335740204622</v>
+        <v>48.05347592769979</v>
       </c>
       <c r="E124" t="n">
-        <v>48.11842123533103</v>
+        <v>48.77024744207435</v>
       </c>
       <c r="F124" t="n">
-        <v>12049800</v>
+        <v>3845900</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>48.47759246826172</v>
+        <v>48.29239654541016</v>
       </c>
       <c r="C125" t="n">
-        <v>48.63290699791971</v>
+        <v>48.82997517352474</v>
       </c>
       <c r="D125" t="n">
-        <v>47.6136551656022</v>
+        <v>48.06342871438038</v>
       </c>
       <c r="E125" t="n">
-        <v>47.84662881158444</v>
+        <v>48.56118585946745</v>
       </c>
       <c r="F125" t="n">
-        <v>10274800</v>
+        <v>4334800</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="B126" t="n">
-        <v>48.3416862487793</v>
+        <v>48.03356552124023</v>
       </c>
       <c r="C126" t="n">
-        <v>48.73967990920678</v>
+        <v>48.87975116682883</v>
       </c>
       <c r="D126" t="n">
-        <v>47.86603718540961</v>
+        <v>47.93401560914242</v>
       </c>
       <c r="E126" t="n">
-        <v>48.53583031061977</v>
+        <v>48.29239757124599</v>
       </c>
       <c r="F126" t="n">
-        <v>10202400</v>
+        <v>4801300</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46009</v>
+        <v>46027</v>
       </c>
       <c r="B127" t="n">
-        <v>48.53583526611328</v>
+        <v>47.86432647705078</v>
       </c>
       <c r="C127" t="n">
-        <v>49.17650814350636</v>
+        <v>48.64082636894248</v>
       </c>
       <c r="D127" t="n">
-        <v>48.11842678658548</v>
+        <v>47.83445846749579</v>
       </c>
       <c r="E127" t="n">
-        <v>48.18637665971881</v>
+        <v>48.04351554645348</v>
       </c>
       <c r="F127" t="n">
-        <v>5144100</v>
+        <v>4531300</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="B128" t="n">
-        <v>48.26403427124023</v>
+        <v>47.95392227172852</v>
       </c>
       <c r="C128" t="n">
-        <v>49.23475094634649</v>
+        <v>48.46163669416705</v>
       </c>
       <c r="D128" t="n">
-        <v>47.85633134214068</v>
+        <v>47.38647942141653</v>
       </c>
       <c r="E128" t="n">
-        <v>48.53583375531311</v>
+        <v>48.31230802931203</v>
       </c>
       <c r="F128" t="n">
-        <v>12839100</v>
+        <v>5168600</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="B129" t="n">
-        <v>47.44621276855469</v>
+        <v>47.48603057861328</v>
       </c>
       <c r="C129" t="n">
-        <v>48.63087345294175</v>
+        <v>47.82450557618741</v>
       </c>
       <c r="D129" t="n">
-        <v>46.96836634634178</v>
+        <v>47.31679118103347</v>
       </c>
       <c r="E129" t="n">
-        <v>48.48154858214222</v>
+        <v>47.78468409468798</v>
       </c>
       <c r="F129" t="n">
-        <v>6391700</v>
+        <v>4904900</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="B130" t="n">
-        <v>48.06343078613281</v>
+        <v>45.50495910644531</v>
       </c>
       <c r="C130" t="n">
-        <v>48.06343078613281</v>
+        <v>47.5955414777012</v>
       </c>
       <c r="D130" t="n">
-        <v>47.50594519005993</v>
+        <v>45.45518414946951</v>
       </c>
       <c r="E130" t="n">
-        <v>47.59554163194105</v>
+        <v>47.33670562528975</v>
       </c>
       <c r="F130" t="n">
-        <v>4886100</v>
+        <v>9557100</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46017</v>
+        <v>46031</v>
       </c>
       <c r="B131" t="n">
-        <v>48.53132247924805</v>
+        <v>45.89320755004883</v>
       </c>
       <c r="C131" t="n">
-        <v>48.53132247924805</v>
+        <v>46.17195413542971</v>
       </c>
       <c r="D131" t="n">
-        <v>47.76477600694246</v>
+        <v>45.45518262671553</v>
       </c>
       <c r="E131" t="n">
-        <v>47.80459749065369</v>
+        <v>45.54477906530481</v>
       </c>
       <c r="F131" t="n">
-        <v>1829300</v>
+        <v>4871300</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46020</v>
+        <v>46034</v>
       </c>
       <c r="B132" t="n">
-        <v>48.49150085449219</v>
+        <v>46.5402946472168</v>
       </c>
       <c r="C132" t="n">
-        <v>48.83993313957347</v>
+        <v>46.77921975591565</v>
       </c>
       <c r="D132" t="n">
-        <v>48.05347592769979</v>
+        <v>45.60451254978332</v>
       </c>
       <c r="E132" t="n">
-        <v>48.77024744207435</v>
+        <v>45.72397320533985</v>
       </c>
       <c r="F132" t="n">
-        <v>3845900</v>
+        <v>4361500</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46021</v>
+        <v>46035</v>
       </c>
       <c r="B133" t="n">
-        <v>48.29239654541016</v>
+        <v>46.19186782836914</v>
       </c>
       <c r="C133" t="n">
-        <v>48.82997517352474</v>
+        <v>46.55024980803837</v>
       </c>
       <c r="D133" t="n">
-        <v>48.06342871438038</v>
+        <v>45.60451420399787</v>
       </c>
       <c r="E133" t="n">
-        <v>48.56118585946745</v>
+        <v>46.5004748495498</v>
       </c>
       <c r="F133" t="n">
-        <v>4334800</v>
+        <v>5294900</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46024</v>
+        <v>46036</v>
       </c>
       <c r="B134" t="n">
-        <v>48.03356552124023</v>
+        <v>46.79912567138672</v>
       </c>
       <c r="C134" t="n">
-        <v>48.87975116682883</v>
+        <v>46.8887221104803</v>
       </c>
       <c r="D134" t="n">
-        <v>47.93401560914242</v>
+        <v>45.8633435945315</v>
       </c>
       <c r="E134" t="n">
-        <v>48.29239757124599</v>
+        <v>46.24164009265837</v>
       </c>
       <c r="F134" t="n">
-        <v>4801300</v>
+        <v>6175000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="B135" t="n">
-        <v>47.86432647705078</v>
+        <v>46.23168182373047</v>
       </c>
       <c r="C135" t="n">
-        <v>48.64082636894248</v>
+        <v>47.13759966716908</v>
       </c>
       <c r="D135" t="n">
-        <v>47.83445846749579</v>
+        <v>46.02262473622593</v>
       </c>
       <c r="E135" t="n">
-        <v>48.04351554645348</v>
+        <v>47.13759966716908</v>
       </c>
       <c r="F135" t="n">
-        <v>4531300</v>
+        <v>4604100</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="B136" t="n">
-        <v>47.95392227172852</v>
+        <v>46.11222076416016</v>
       </c>
       <c r="C136" t="n">
-        <v>48.46163669416705</v>
+        <v>46.87876720912635</v>
       </c>
       <c r="D136" t="n">
-        <v>47.38647942141653</v>
+        <v>45.29589936512303</v>
       </c>
       <c r="E136" t="n">
-        <v>48.31230802931203</v>
+        <v>46.44074229668234</v>
       </c>
       <c r="F136" t="n">
-        <v>5168600</v>
+        <v>9477300</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="B137" t="n">
-        <v>47.48603057861328</v>
+        <v>46.01266860961914</v>
       </c>
       <c r="C137" t="n">
-        <v>47.82450557618741</v>
+        <v>46.53033646137187</v>
       </c>
       <c r="D137" t="n">
-        <v>47.31679118103347</v>
+        <v>45.59455066114812</v>
       </c>
       <c r="E137" t="n">
-        <v>47.78468409468798</v>
+        <v>46.12217578178025</v>
       </c>
       <c r="F137" t="n">
-        <v>4904900</v>
+        <v>5052000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>45.50495910644531</v>
+        <v>46.22172927856445</v>
       </c>
       <c r="C138" t="n">
-        <v>47.5955414777012</v>
+        <v>47.06791491500173</v>
       </c>
       <c r="D138" t="n">
-        <v>45.45518414946951</v>
+        <v>45.79365782551905</v>
       </c>
       <c r="E138" t="n">
-        <v>47.33670562528975</v>
+        <v>46.33123645923919</v>
       </c>
       <c r="F138" t="n">
-        <v>9557100</v>
+        <v>5987900</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>45.89320755004883</v>
+        <v>47.37652587890625</v>
       </c>
       <c r="C139" t="n">
-        <v>46.17195413542971</v>
+        <v>47.77473311953753</v>
       </c>
       <c r="D139" t="n">
-        <v>45.45518262671553</v>
+        <v>46.44074380028416</v>
       </c>
       <c r="E139" t="n">
-        <v>45.54477906530481</v>
+        <v>46.78917228764725</v>
       </c>
       <c r="F139" t="n">
-        <v>4871300</v>
+        <v>7600400</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>46.5402946472168</v>
+        <v>49.00917053222656</v>
       </c>
       <c r="C140" t="n">
-        <v>46.77921975591565</v>
+        <v>49.32773481741299</v>
       </c>
       <c r="D140" t="n">
-        <v>45.60451254978332</v>
+        <v>47.35661687872729</v>
       </c>
       <c r="E140" t="n">
-        <v>45.72397320533985</v>
+        <v>47.68513843396782</v>
       </c>
       <c r="F140" t="n">
-        <v>4361500</v>
+        <v>14397700</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>46.19186782836914</v>
+        <v>49.64629745483398</v>
       </c>
       <c r="C141" t="n">
-        <v>46.55024980803837</v>
+        <v>50.96037603701006</v>
       </c>
       <c r="D141" t="n">
-        <v>45.60451420399787</v>
+        <v>48.94943668002287</v>
       </c>
       <c r="E141" t="n">
-        <v>46.5004748495498</v>
+        <v>49.12862955919103</v>
       </c>
       <c r="F141" t="n">
-        <v>5294900</v>
+        <v>9064000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46036</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>46.79912567138672</v>
+        <v>51.37849044799805</v>
       </c>
       <c r="C142" t="n">
-        <v>46.8887221104803</v>
+        <v>51.51786183375104</v>
       </c>
       <c r="D142" t="n">
-        <v>45.8633435945315</v>
+        <v>49.77571191666767</v>
       </c>
       <c r="E142" t="n">
-        <v>46.24164009265837</v>
+        <v>49.77571191666767</v>
       </c>
       <c r="F142" t="n">
-        <v>6175000</v>
+        <v>14664900</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>46.23168182373047</v>
+        <v>52.46360397338867</v>
       </c>
       <c r="C143" t="n">
-        <v>47.13759966716908</v>
+        <v>52.84190046785632</v>
       </c>
       <c r="D143" t="n">
-        <v>46.02262473622593</v>
+        <v>51.35858250111847</v>
       </c>
       <c r="E143" t="n">
-        <v>47.13759966716908</v>
+        <v>51.76674320913321</v>
       </c>
       <c r="F143" t="n">
-        <v>4604100</v>
+        <v>11316600</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>46.11222076416016</v>
+        <v>51.33867263793945</v>
       </c>
       <c r="C144" t="n">
-        <v>46.87876720912635</v>
+        <v>52.76225840435436</v>
       </c>
       <c r="D144" t="n">
-        <v>45.29589936512303</v>
+        <v>50.49248699388504</v>
       </c>
       <c r="E144" t="n">
-        <v>46.44074229668234</v>
+        <v>52.46360487101667</v>
       </c>
       <c r="F144" t="n">
-        <v>9477300</v>
+        <v>13110700</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>46.01266860961914</v>
+        <v>51.83642959594727</v>
       </c>
       <c r="C145" t="n">
-        <v>46.53033646137187</v>
+        <v>53.15050817571397</v>
       </c>
       <c r="D145" t="n">
-        <v>45.59455066114812</v>
+        <v>51.35858318490353</v>
       </c>
       <c r="E145" t="n">
-        <v>46.12217578178025</v>
+        <v>51.83642959594727</v>
       </c>
       <c r="F145" t="n">
-        <v>5052000</v>
+        <v>9387700</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>46.22172927856445</v>
+        <v>51.48800277709961</v>
       </c>
       <c r="C146" t="n">
-        <v>47.06791491500173</v>
+        <v>52.06539911840073</v>
       </c>
       <c r="D146" t="n">
-        <v>45.79365782551905</v>
+        <v>51.2988526224228</v>
       </c>
       <c r="E146" t="n">
-        <v>46.33123645923919</v>
+        <v>51.86629549128158</v>
       </c>
       <c r="F146" t="n">
-        <v>5987900</v>
+        <v>7212600</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>47.37652587890625</v>
+        <v>51.71696853637695</v>
       </c>
       <c r="C147" t="n">
-        <v>47.77473311953753</v>
+        <v>52.1549934603302</v>
       </c>
       <c r="D147" t="n">
-        <v>46.44074380028416</v>
+        <v>51.08979346536439</v>
       </c>
       <c r="E147" t="n">
-        <v>46.78917228764725</v>
+        <v>51.53777565894479</v>
       </c>
       <c r="F147" t="n">
-        <v>7600400</v>
+        <v>6846500</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46044</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>49.00917053222656</v>
+        <v>53.75777435302734</v>
       </c>
       <c r="C148" t="n">
-        <v>49.32773481741299</v>
+        <v>53.75777435302734</v>
       </c>
       <c r="D148" t="n">
-        <v>47.35661687872729</v>
+        <v>52.00567078579237</v>
       </c>
       <c r="E148" t="n">
-        <v>47.68513843396782</v>
+        <v>52.56315638566513</v>
       </c>
       <c r="F148" t="n">
-        <v>14397700</v>
+        <v>6917500</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46045</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>49.64629745483398</v>
+        <v>51.16943359375</v>
       </c>
       <c r="C149" t="n">
-        <v>50.96037603701006</v>
+        <v>53.21023703176535</v>
       </c>
       <c r="D149" t="n">
-        <v>48.94943668002287</v>
+        <v>50.96037271661832</v>
       </c>
       <c r="E149" t="n">
-        <v>49.12862955919103</v>
+        <v>53.20027976269051</v>
       </c>
       <c r="F149" t="n">
-        <v>9064000</v>
+        <v>8893000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46048</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>51.37849044799805</v>
+        <v>51.97580337524414</v>
       </c>
       <c r="C150" t="n">
-        <v>51.51786183375104</v>
+        <v>53.03104995486049</v>
       </c>
       <c r="D150" t="n">
-        <v>49.77571191666767</v>
+        <v>51.19930339637857</v>
       </c>
       <c r="E150" t="n">
-        <v>49.77571191666767</v>
+        <v>51.21921413911689</v>
       </c>
       <c r="F150" t="n">
-        <v>14664900</v>
+        <v>7437700</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>52.46360397338867</v>
+        <v>51.61741256713867</v>
       </c>
       <c r="C151" t="n">
-        <v>52.84190046785632</v>
+        <v>52.56315186825393</v>
       </c>
       <c r="D151" t="n">
-        <v>51.35858250111847</v>
+        <v>51.26898409716303</v>
       </c>
       <c r="E151" t="n">
-        <v>51.76674320913321</v>
+        <v>52.13508043509214</v>
       </c>
       <c r="F151" t="n">
-        <v>11316600</v>
+        <v>5766400</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>51.33867263793945</v>
+        <v>53.50889205932617</v>
       </c>
       <c r="C152" t="n">
-        <v>52.76225840435436</v>
+        <v>53.64826344963445</v>
       </c>
       <c r="D152" t="n">
-        <v>50.49248699388504</v>
+        <v>51.47804203532842</v>
       </c>
       <c r="E152" t="n">
-        <v>52.46360487101667</v>
+        <v>51.7667420853016</v>
       </c>
       <c r="F152" t="n">
-        <v>13110700</v>
+        <v>7661100</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46051</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>51.83642959594727</v>
+        <v>52.16495132446289</v>
       </c>
       <c r="C153" t="n">
-        <v>53.15050817571397</v>
+        <v>53.73786195835529</v>
       </c>
       <c r="D153" t="n">
-        <v>51.35858318490353</v>
+        <v>51.78665482361861</v>
       </c>
       <c r="E153" t="n">
-        <v>51.83642959594727</v>
+        <v>53.45911916698883</v>
       </c>
       <c r="F153" t="n">
-        <v>9387700</v>
+        <v>8866200</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>51.48800277709961</v>
+        <v>53.34961318969727</v>
       </c>
       <c r="C154" t="n">
-        <v>52.06539911840073</v>
+        <v>53.73786317146102</v>
       </c>
       <c r="D154" t="n">
-        <v>51.2988526224228</v>
+        <v>52.39392034265019</v>
       </c>
       <c r="E154" t="n">
-        <v>51.86629549128158</v>
+        <v>52.81203453913861</v>
       </c>
       <c r="F154" t="n">
-        <v>7212600</v>
+        <v>6680100</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>51.71696853637695</v>
+        <v>53.78763580322266</v>
       </c>
       <c r="C155" t="n">
-        <v>52.1549934603302</v>
+        <v>53.8274572861912</v>
       </c>
       <c r="D155" t="n">
-        <v>51.08979346536439</v>
+        <v>52.35409659462578</v>
       </c>
       <c r="E155" t="n">
-        <v>51.53777565894479</v>
+        <v>53.02108934521354</v>
       </c>
       <c r="F155" t="n">
-        <v>6846500</v>
+        <v>6660500</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>53.75777435302734</v>
+        <v>53.55867004394531</v>
       </c>
       <c r="C156" t="n">
-        <v>53.75777435302734</v>
+        <v>54.27544157475813</v>
       </c>
       <c r="D156" t="n">
-        <v>52.00567078579237</v>
+        <v>52.91158800981554</v>
       </c>
       <c r="E156" t="n">
-        <v>52.56315638566513</v>
+        <v>53.00118445116714</v>
       </c>
       <c r="F156" t="n">
-        <v>6917500</v>
+        <v>7178500</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="B157" t="n">
-        <v>51.16943359375</v>
+        <v>53.15050888061523</v>
       </c>
       <c r="C157" t="n">
-        <v>53.21023703176535</v>
+        <v>54.2853945965936</v>
       </c>
       <c r="D157" t="n">
-        <v>50.96037271661832</v>
+        <v>53.00118401132563</v>
       </c>
       <c r="E157" t="n">
-        <v>53.20027976269051</v>
+        <v>54.2853945965936</v>
       </c>
       <c r="F157" t="n">
-        <v>8893000</v>
+        <v>7766100</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46058</v>
+        <v>46072</v>
       </c>
       <c r="B158" t="n">
-        <v>51.97580337524414</v>
+        <v>51.13957214355469</v>
       </c>
       <c r="C158" t="n">
-        <v>53.03104995486049</v>
+        <v>53.75777600100161</v>
       </c>
       <c r="D158" t="n">
-        <v>51.19930339637857</v>
+        <v>50.62190421524213</v>
       </c>
       <c r="E158" t="n">
-        <v>51.21921413911689</v>
+        <v>53.1903331136868</v>
       </c>
       <c r="F158" t="n">
-        <v>7437700</v>
+        <v>11680200</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B159" t="n">
-        <v>51.61741256713867</v>
+        <v>51.75679016113281</v>
       </c>
       <c r="C159" t="n">
-        <v>52.56315186825393</v>
+        <v>52.36405069455032</v>
       </c>
       <c r="D159" t="n">
-        <v>51.26898409716303</v>
+        <v>49.67616512089494</v>
       </c>
       <c r="E159" t="n">
-        <v>52.13508043509214</v>
+        <v>50.97033295220784</v>
       </c>
       <c r="F159" t="n">
-        <v>5766400</v>
+        <v>14808500</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="B160" t="n">
-        <v>53.50889205932617</v>
+        <v>51.73688125610352</v>
       </c>
       <c r="C160" t="n">
-        <v>53.64826344963445</v>
+        <v>52.19481693923368</v>
       </c>
       <c r="D160" t="n">
-        <v>51.47804203532842</v>
+        <v>50.99024550411858</v>
       </c>
       <c r="E160" t="n">
-        <v>51.7667420853016</v>
+        <v>51.30880978782529</v>
       </c>
       <c r="F160" t="n">
-        <v>7661100</v>
+        <v>5164300</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="B161" t="n">
-        <v>52.16495132446289</v>
+        <v>51.17938995361328</v>
       </c>
       <c r="C161" t="n">
-        <v>53.73786195835529</v>
+        <v>51.97580063320164</v>
       </c>
       <c r="D161" t="n">
-        <v>51.78665482361861</v>
+        <v>51.00019707600769</v>
       </c>
       <c r="E161" t="n">
-        <v>53.45911916698883</v>
+        <v>51.73687932811797</v>
       </c>
       <c r="F161" t="n">
-        <v>8866200</v>
+        <v>11974100</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="B162" t="n">
-        <v>53.34961318969727</v>
+        <v>50.05445861816406</v>
       </c>
       <c r="C162" t="n">
-        <v>53.73786317146102</v>
+        <v>51.18934433135516</v>
       </c>
       <c r="D162" t="n">
-        <v>52.39392034265019</v>
+        <v>49.73589434069238</v>
       </c>
       <c r="E162" t="n">
-        <v>52.81203453913861</v>
+        <v>50.90064806573664</v>
       </c>
       <c r="F162" t="n">
-        <v>6680100</v>
+        <v>10719400</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46065</v>
+        <v>46079</v>
       </c>
       <c r="B163" t="n">
-        <v>53.78763580322266</v>
+        <v>49.15849685668945</v>
       </c>
       <c r="C163" t="n">
-        <v>53.8274572861912</v>
+        <v>49.76576118309524</v>
       </c>
       <c r="D163" t="n">
-        <v>52.35409659462578</v>
+        <v>47.89419324873992</v>
       </c>
       <c r="E163" t="n">
-        <v>53.02108934521354</v>
+        <v>49.67616474481265</v>
       </c>
       <c r="F163" t="n">
-        <v>6660500</v>
+        <v>9902400</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="B164" t="n">
-        <v>53.55867004394531</v>
+        <v>49.4770622253418</v>
       </c>
       <c r="C164" t="n">
-        <v>54.27544157475813</v>
+        <v>49.57661213782828</v>
       </c>
       <c r="D164" t="n">
-        <v>52.91158800981554</v>
+        <v>48.49150138234841</v>
       </c>
       <c r="E164" t="n">
-        <v>53.00118445116714</v>
+        <v>49.09876572223885</v>
       </c>
       <c r="F164" t="n">
-        <v>7178500</v>
+        <v>7316400</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46071</v>
+        <v>46083</v>
       </c>
       <c r="B165" t="n">
-        <v>53.15050888061523</v>
+        <v>48.47159194946289</v>
       </c>
       <c r="C165" t="n">
-        <v>54.2853945965936</v>
+        <v>49.07885630575443</v>
       </c>
       <c r="D165" t="n">
-        <v>53.00118401132563</v>
+        <v>48.21275989145602</v>
       </c>
       <c r="E165" t="n">
-        <v>54.2853945965936</v>
+        <v>49.07885630575443</v>
       </c>
       <c r="F165" t="n">
-        <v>7766100</v>
+        <v>5402000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46072</v>
+        <v>46084</v>
       </c>
       <c r="B166" t="n">
-        <v>51.13957214355469</v>
+        <v>47.18738174438477</v>
       </c>
       <c r="C166" t="n">
-        <v>53.75777600100161</v>
+        <v>47.963881722739</v>
       </c>
       <c r="D166" t="n">
-        <v>50.62190421524213</v>
+        <v>45.84343509232643</v>
       </c>
       <c r="E166" t="n">
-        <v>53.1903331136868</v>
+        <v>47.00818885744366</v>
       </c>
       <c r="F166" t="n">
-        <v>11680200</v>
+        <v>13648400</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46073</v>
+        <v>46085</v>
       </c>
       <c r="B167" t="n">
-        <v>51.75679016113281</v>
+        <v>47.12764739990234</v>
       </c>
       <c r="C167" t="n">
-        <v>52.36405069455032</v>
+        <v>48.00370105254275</v>
       </c>
       <c r="D167" t="n">
-        <v>49.67616512089494</v>
+        <v>46.60997950505054</v>
       </c>
       <c r="E167" t="n">
-        <v>50.97033295220784</v>
+        <v>47.78468668998622</v>
       </c>
       <c r="F167" t="n">
-        <v>14808500</v>
+        <v>6449100</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="B168" t="n">
-        <v>51.73688125610352</v>
+        <v>46.50047302246094</v>
       </c>
       <c r="C168" t="n">
-        <v>52.19481693923368</v>
+        <v>47.2570660330685</v>
       </c>
       <c r="D168" t="n">
-        <v>50.99024550411858</v>
+        <v>46.27150518434137</v>
       </c>
       <c r="E168" t="n">
-        <v>51.30880978782529</v>
+        <v>46.88872300003698</v>
       </c>
       <c r="F168" t="n">
-        <v>5164300</v>
+        <v>7897500</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="B169" t="n">
-        <v>51.17938995361328</v>
+        <v>46.4108772277832</v>
       </c>
       <c r="C169" t="n">
-        <v>51.97580063320164</v>
+        <v>47.13760223651968</v>
       </c>
       <c r="D169" t="n">
-        <v>51.00019707600769</v>
+        <v>45.97285228757632</v>
       </c>
       <c r="E169" t="n">
-        <v>51.73687932811797</v>
+        <v>46.39096648537573</v>
       </c>
       <c r="F169" t="n">
-        <v>11974100</v>
+        <v>5517900</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="B170" t="n">
-        <v>50.05445861816406</v>
+        <v>46.37105941772461</v>
       </c>
       <c r="C170" t="n">
-        <v>51.18934433135516</v>
+        <v>47.02809872508745</v>
       </c>
       <c r="D170" t="n">
-        <v>49.73589434069238</v>
+        <v>45.66424135568204</v>
       </c>
       <c r="E170" t="n">
-        <v>50.90064806573664</v>
+        <v>46.33123793301515</v>
       </c>
       <c r="F170" t="n">
-        <v>10719400</v>
+        <v>5742300</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="B171" t="n">
-        <v>49.15849685668945</v>
+        <v>46.97832107543945</v>
       </c>
       <c r="C171" t="n">
-        <v>49.76576118309524</v>
+        <v>47.73491411237264</v>
       </c>
       <c r="D171" t="n">
-        <v>47.89419324873992</v>
+        <v>45.99276399000566</v>
       </c>
       <c r="E171" t="n">
-        <v>49.67616474481265</v>
+        <v>46.80908545782217</v>
       </c>
       <c r="F171" t="n">
-        <v>9902400</v>
+        <v>5655000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46080</v>
+        <v>46092</v>
       </c>
       <c r="B172" t="n">
-        <v>49.4770622253418</v>
+        <v>46.66971206665039</v>
       </c>
       <c r="C172" t="n">
-        <v>49.57661213782828</v>
+        <v>47.36657284541516</v>
       </c>
       <c r="D172" t="n">
-        <v>48.49150138234841</v>
+        <v>46.39096547659305</v>
       </c>
       <c r="E172" t="n">
-        <v>49.09876572223885</v>
+        <v>46.78917272091169</v>
       </c>
       <c r="F172" t="n">
-        <v>7316400</v>
+        <v>3420400</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="B173" t="n">
-        <v>48.47159194946289</v>
+        <v>45.61446380615234</v>
       </c>
       <c r="C173" t="n">
-        <v>49.07885630575443</v>
+        <v>46.59006734057215</v>
       </c>
       <c r="D173" t="n">
-        <v>48.21275989145602</v>
+        <v>44.8777853688245</v>
       </c>
       <c r="E173" t="n">
-        <v>49.07885630575443</v>
+        <v>46.52038164508399</v>
       </c>
       <c r="F173" t="n">
-        <v>5402000</v>
+        <v>7215300</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="B174" t="n">
-        <v>47.18738174438477</v>
+        <v>46.00271606445312</v>
       </c>
       <c r="C174" t="n">
-        <v>47.963881722739</v>
+        <v>46.67966610951933</v>
       </c>
       <c r="D174" t="n">
-        <v>45.84343509232643</v>
+        <v>45.70406252635586</v>
       </c>
       <c r="E174" t="n">
-        <v>47.00818885744366</v>
+        <v>46.29141613023431</v>
       </c>
       <c r="F174" t="n">
-        <v>13648400</v>
+        <v>4406200</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B175" t="n">
-        <v>47.12764739990234</v>
+        <v>45.7637939453125</v>
       </c>
       <c r="C175" t="n">
-        <v>48.00370105254275</v>
+        <v>47.00818683007662</v>
       </c>
       <c r="D175" t="n">
-        <v>46.60997950505054</v>
+        <v>45.3556332310133</v>
       </c>
       <c r="E175" t="n">
-        <v>47.78468668998622</v>
+        <v>47.00818683007662</v>
       </c>
       <c r="F175" t="n">
-        <v>6449100</v>
+        <v>5913000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="B176" t="n">
-        <v>46.50047302246094</v>
+        <v>45.99276351928711</v>
       </c>
       <c r="C176" t="n">
-        <v>47.2570660330685</v>
+        <v>47.05796356511127</v>
       </c>
       <c r="D176" t="n">
-        <v>46.27150518434137</v>
+        <v>45.53482783180091</v>
       </c>
       <c r="E176" t="n">
-        <v>46.88872300003698</v>
+        <v>45.63437774731153</v>
       </c>
       <c r="F176" t="n">
-        <v>7897500</v>
+        <v>5780200</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="B177" t="n">
-        <v>46.4108772277832</v>
+        <v>45.95294189453125</v>
       </c>
       <c r="C177" t="n">
-        <v>47.13760223651968</v>
+        <v>46.54029550846667</v>
       </c>
       <c r="D177" t="n">
-        <v>45.97285228757632</v>
+        <v>45.72397405148332</v>
       </c>
       <c r="E177" t="n">
-        <v>46.39096648537573</v>
+        <v>45.94298842204475</v>
       </c>
       <c r="F177" t="n">
-        <v>5517900</v>
+        <v>5688200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="B178" t="n">
-        <v>46.37105941772461</v>
+        <v>46.38101196289062</v>
       </c>
       <c r="C178" t="n">
-        <v>47.02809872508745</v>
+        <v>46.60997979901393</v>
       </c>
       <c r="D178" t="n">
-        <v>45.66424135568204</v>
+        <v>44.7483690982996</v>
       </c>
       <c r="E178" t="n">
-        <v>46.33123793301515</v>
+        <v>44.79814405439845</v>
       </c>
       <c r="F178" t="n">
-        <v>5742300</v>
+        <v>5299300</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="B179" t="n">
-        <v>46.97832107543945</v>
+        <v>45.75383758544922</v>
       </c>
       <c r="C179" t="n">
-        <v>47.73491411237264</v>
+        <v>46.32128044837899</v>
       </c>
       <c r="D179" t="n">
-        <v>45.99276399000566</v>
+        <v>45.2361696793827</v>
       </c>
       <c r="E179" t="n">
-        <v>46.80908545782217</v>
+        <v>46.2914162337782</v>
       </c>
       <c r="F179" t="n">
-        <v>5655000</v>
+        <v>10234300</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46092</v>
+        <v>46104</v>
       </c>
       <c r="B180" t="n">
-        <v>46.66971206665039</v>
+        <v>47.14074325561523</v>
       </c>
       <c r="C180" t="n">
-        <v>47.36657284541516</v>
+        <v>47.69944973098251</v>
       </c>
       <c r="D180" t="n">
-        <v>46.39096547659305</v>
+        <v>46.17298498042371</v>
       </c>
       <c r="E180" t="n">
-        <v>46.78917272091169</v>
+        <v>46.41243170011726</v>
       </c>
       <c r="F180" t="n">
-        <v>3420400</v>
+        <v>5584500</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="B181" t="n">
-        <v>45.61446380615234</v>
+        <v>47.34028244018555</v>
       </c>
       <c r="C181" t="n">
-        <v>46.59006734057215</v>
+        <v>47.49991232100932</v>
       </c>
       <c r="D181" t="n">
-        <v>44.8777853688245</v>
+        <v>46.41243256856095</v>
       </c>
       <c r="E181" t="n">
-        <v>46.52038164508399</v>
+        <v>47.1407441376867</v>
       </c>
       <c r="F181" t="n">
-        <v>7215300</v>
+        <v>5779900</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="B182" t="n">
-        <v>46.00271606445312</v>
+        <v>48.0685920715332</v>
       </c>
       <c r="C182" t="n">
-        <v>46.67966610951933</v>
+        <v>48.85676624139808</v>
       </c>
       <c r="D182" t="n">
-        <v>45.70406252635586</v>
+        <v>47.55976923037935</v>
       </c>
       <c r="E182" t="n">
-        <v>46.29141613023431</v>
+        <v>48.16835931582246</v>
       </c>
       <c r="F182" t="n">
-        <v>4406200</v>
+        <v>8453500</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="B183" t="n">
-        <v>45.7637939453125</v>
+        <v>47.41011810302734</v>
       </c>
       <c r="C183" t="n">
-        <v>47.00818683007662</v>
+        <v>48.2381968825248</v>
       </c>
       <c r="D183" t="n">
-        <v>45.3556332310133</v>
+        <v>47.19062559974726</v>
       </c>
       <c r="E183" t="n">
-        <v>47.00818683007662</v>
+        <v>47.67949422817752</v>
       </c>
       <c r="F183" t="n">
-        <v>5913000</v>
+        <v>4612800</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="B184" t="n">
-        <v>45.99276351928711</v>
+        <v>47.30037307739258</v>
       </c>
       <c r="C184" t="n">
-        <v>47.05796356511127</v>
+        <v>47.56974920952486</v>
       </c>
       <c r="D184" t="n">
-        <v>45.53482783180091</v>
+        <v>46.81150443629105</v>
       </c>
       <c r="E184" t="n">
-        <v>45.63437774731153</v>
+        <v>47.43007354231771</v>
       </c>
       <c r="F184" t="n">
-        <v>5780200</v>
+        <v>3314900</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46099</v>
+        <v>46111</v>
       </c>
       <c r="B185" t="n">
-        <v>45.95294189453125</v>
+        <v>48.93658065795898</v>
       </c>
       <c r="C185" t="n">
-        <v>46.54029550846667</v>
+        <v>49.6449380077002</v>
       </c>
       <c r="D185" t="n">
-        <v>45.72397405148332</v>
+        <v>48.26813172941132</v>
       </c>
       <c r="E185" t="n">
-        <v>45.94298842204475</v>
+        <v>48.64725031312051</v>
       </c>
       <c r="F185" t="n">
-        <v>5688200</v>
+        <v>8682700</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="B186" t="n">
-        <v>46.38101196289062</v>
+        <v>50.89204788208008</v>
       </c>
       <c r="C186" t="n">
-        <v>46.60997979901393</v>
+        <v>51.23126185217961</v>
       </c>
       <c r="D186" t="n">
-        <v>44.7483690982996</v>
+        <v>49.30572428747885</v>
       </c>
       <c r="E186" t="n">
-        <v>44.79814405439845</v>
+        <v>49.45537896476966</v>
       </c>
       <c r="F186" t="n">
-        <v>5299300</v>
+        <v>11795500</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="B187" t="n">
-        <v>45.75383758544922</v>
+        <v>50.89204788208008</v>
       </c>
       <c r="C187" t="n">
-        <v>46.32128044837899</v>
+        <v>51.53057120676124</v>
       </c>
       <c r="D187" t="n">
-        <v>45.2361696793827</v>
+        <v>50.6326507547694</v>
       </c>
       <c r="E187" t="n">
-        <v>46.2914162337782</v>
+        <v>51.25121606287681</v>
       </c>
       <c r="F187" t="n">
-        <v>10234300</v>
+        <v>12831600</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46104</v>
+        <v>46114</v>
       </c>
       <c r="B188" t="n">
-        <v>47.14074325561523</v>
+        <v>50.19366836547852</v>
       </c>
       <c r="C188" t="n">
-        <v>47.69944973098251</v>
+        <v>51.37094012799928</v>
       </c>
       <c r="D188" t="n">
-        <v>46.17298498042371</v>
+        <v>49.28577273226773</v>
       </c>
       <c r="E188" t="n">
-        <v>46.41243170011726</v>
+        <v>49.38553997754856</v>
       </c>
       <c r="F188" t="n">
-        <v>5584500</v>
+        <v>7547300</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46105</v>
+        <v>46118</v>
       </c>
       <c r="B189" t="n">
-        <v>47.34028244018555</v>
+        <v>50.50294876098633</v>
       </c>
       <c r="C189" t="n">
-        <v>47.49991232100932</v>
+        <v>50.79227909853186</v>
       </c>
       <c r="D189" t="n">
-        <v>46.41243256856095</v>
+        <v>49.95422130397419</v>
       </c>
       <c r="E189" t="n">
-        <v>47.1407441376867</v>
+        <v>50.19366801922342</v>
       </c>
       <c r="F189" t="n">
-        <v>5779900</v>
+        <v>2617700</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="B190" t="n">
-        <v>48.0685920715332</v>
+        <v>50.53288269042969</v>
       </c>
       <c r="C190" t="n">
-        <v>48.85676624139808</v>
+        <v>50.62267473417762</v>
       </c>
       <c r="D190" t="n">
-        <v>47.55976923037935</v>
+        <v>49.42544875283066</v>
       </c>
       <c r="E190" t="n">
-        <v>48.16835931582246</v>
+        <v>50.11385188431384</v>
       </c>
       <c r="F190" t="n">
-        <v>8453500</v>
+        <v>3983500</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="B191" t="n">
-        <v>47.41011810302734</v>
+        <v>52.64797973632812</v>
       </c>
       <c r="C191" t="n">
-        <v>48.2381968825248</v>
+        <v>52.77768020137379</v>
       </c>
       <c r="D191" t="n">
-        <v>47.19062559974726</v>
+        <v>51.79994291826216</v>
       </c>
       <c r="E191" t="n">
-        <v>47.67949422817752</v>
+        <v>52.11920647973068</v>
       </c>
       <c r="F191" t="n">
-        <v>4612800</v>
+        <v>10118800</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="B192" t="n">
-        <v>47.30037307739258</v>
+        <v>52.37860488891602</v>
       </c>
       <c r="C192" t="n">
-        <v>47.56974920952486</v>
+        <v>52.74774827677341</v>
       </c>
       <c r="D192" t="n">
-        <v>46.81150443629105</v>
+        <v>51.77999378396476</v>
       </c>
       <c r="E192" t="n">
-        <v>47.43007354231771</v>
+        <v>52.42848851334919</v>
       </c>
       <c r="F192" t="n">
-        <v>3314900</v>
+        <v>6218000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="B193" t="n">
-        <v>48.93658065795898</v>
+        <v>52.75772476196289</v>
       </c>
       <c r="C193" t="n">
-        <v>49.6449380077002</v>
+        <v>53.2166601742013</v>
       </c>
       <c r="D193" t="n">
-        <v>48.26813172941132</v>
+        <v>52.18904309769433</v>
       </c>
       <c r="E193" t="n">
-        <v>48.64725031312051</v>
+        <v>52.37860238382505</v>
       </c>
       <c r="F193" t="n">
-        <v>8682700</v>
+        <v>6331700</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46112</v>
+        <v>46125</v>
       </c>
       <c r="B194" t="n">
-        <v>50.89204788208008</v>
+        <v>51.91967010498047</v>
       </c>
       <c r="C194" t="n">
-        <v>51.23126185217961</v>
+        <v>52.75772794593419</v>
       </c>
       <c r="D194" t="n">
-        <v>49.30572428747885</v>
+        <v>51.91967010498047</v>
       </c>
       <c r="E194" t="n">
-        <v>49.45537896476966</v>
+        <v>52.64798168728078</v>
       </c>
       <c r="F194" t="n">
-        <v>11795500</v>
+        <v>5536700</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="B195" t="n">
-        <v>50.89204788208008</v>
+        <v>51.77999114990234</v>
       </c>
       <c r="C195" t="n">
-        <v>51.53057120676124</v>
+        <v>52.22894755283896</v>
       </c>
       <c r="D195" t="n">
-        <v>50.6326507547694</v>
+        <v>50.47301894333033</v>
       </c>
       <c r="E195" t="n">
-        <v>51.25121606287681</v>
+        <v>52.16908872891482</v>
       </c>
       <c r="F195" t="n">
-        <v>12831600</v>
+        <v>11897600</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="B196" t="n">
-        <v>50.19366836547852</v>
+        <v>49.84447479248047</v>
       </c>
       <c r="C196" t="n">
-        <v>51.37094012799928</v>
+        <v>51.97952578503357</v>
       </c>
       <c r="D196" t="n">
-        <v>49.28577273226773</v>
+        <v>49.19598009424432</v>
       </c>
       <c r="E196" t="n">
-        <v>49.38553997754856</v>
+        <v>51.77999129688484</v>
       </c>
       <c r="F196" t="n">
-        <v>7547300</v>
+        <v>14915400</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="B197" t="n">
-        <v>50.50294876098633</v>
+        <v>48.2880859375</v>
       </c>
       <c r="C197" t="n">
-        <v>50.79227909853186</v>
+        <v>50.13380665002597</v>
       </c>
       <c r="D197" t="n">
-        <v>49.95422130397419</v>
+        <v>48.04863921622764</v>
       </c>
       <c r="E197" t="n">
-        <v>50.19366801922342</v>
+        <v>50.08392302647488</v>
       </c>
       <c r="F197" t="n">
-        <v>2617700</v>
+        <v>10979400</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="B198" t="n">
-        <v>50.53288269042969</v>
+        <v>48.53750610351562</v>
       </c>
       <c r="C198" t="n">
-        <v>50.62267473417762</v>
+        <v>49.83449929826048</v>
       </c>
       <c r="D198" t="n">
-        <v>49.42544875283066</v>
+        <v>48.48761867589451</v>
       </c>
       <c r="E198" t="n">
-        <v>50.11385188431384</v>
+        <v>48.98646250509456</v>
       </c>
       <c r="F198" t="n">
-        <v>3983500</v>
+        <v>9369900</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="B199" t="n">
-        <v>52.64797973632812</v>
+        <v>48.36790084838867</v>
       </c>
       <c r="C199" t="n">
-        <v>52.77768020137379</v>
+        <v>48.90665313772215</v>
       </c>
       <c r="D199" t="n">
-        <v>51.79994291826216</v>
+        <v>48.1284579237138</v>
       </c>
       <c r="E199" t="n">
-        <v>52.11920647973068</v>
+        <v>48.63727699305541</v>
       </c>
       <c r="F199" t="n">
-        <v>10118800</v>
+        <v>4448400</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="B200" t="n">
-        <v>52.37860488891602</v>
+        <v>47.08087921142578</v>
       </c>
       <c r="C200" t="n">
-        <v>52.74774827677341</v>
+        <v>48.81685741095061</v>
       </c>
       <c r="D200" t="n">
-        <v>51.77999378396476</v>
+        <v>46.5121975508296</v>
       </c>
       <c r="E200" t="n">
-        <v>52.42848851334919</v>
+        <v>48.16835891089288</v>
       </c>
       <c r="F200" t="n">
-        <v>6218000</v>
+        <v>10210700</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="B201" t="n">
-        <v>52.75772476196289</v>
+        <v>48.16836166381836</v>
       </c>
       <c r="C201" t="n">
-        <v>53.2166601742013</v>
+        <v>48.93658166109746</v>
       </c>
       <c r="D201" t="n">
-        <v>52.18904309769433</v>
+        <v>47.19062815979313</v>
       </c>
       <c r="E201" t="n">
-        <v>52.37860238382505</v>
+        <v>47.35025804196303</v>
       </c>
       <c r="F201" t="n">
-        <v>6331700</v>
+        <v>10526700</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="B202" t="n">
-        <v>51.91967010498047</v>
+        <v>47.68947219848633</v>
       </c>
       <c r="C202" t="n">
-        <v>52.75772794593419</v>
+        <v>48.51755483192884</v>
       </c>
       <c r="D202" t="n">
-        <v>51.91967010498047</v>
+        <v>47.26046617492301</v>
       </c>
       <c r="E202" t="n">
-        <v>52.64798168728078</v>
+        <v>48.51755483192884</v>
       </c>
       <c r="F202" t="n">
-        <v>5536700</v>
+        <v>5113600</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="B203" t="n">
-        <v>51.77999114990234</v>
+        <v>48.07856750488281</v>
       </c>
       <c r="C203" t="n">
-        <v>52.22894755283896</v>
+        <v>48.39782725519584</v>
       </c>
       <c r="D203" t="n">
-        <v>50.47301894333033</v>
+        <v>47.50988583677047</v>
       </c>
       <c r="E203" t="n">
-        <v>52.16908872891482</v>
+        <v>47.76928676257256</v>
       </c>
       <c r="F203" t="n">
-        <v>11897600</v>
+        <v>5188300</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="B204" t="n">
-        <v>49.84447479248047</v>
+        <v>47.1806526184082</v>
       </c>
       <c r="C204" t="n">
-        <v>51.97952578503357</v>
+        <v>47.88900997758291</v>
       </c>
       <c r="D204" t="n">
-        <v>49.19598009424432</v>
+        <v>46.90129747220957</v>
       </c>
       <c r="E204" t="n">
-        <v>51.77999129688484</v>
+        <v>47.58970442639833</v>
       </c>
       <c r="F204" t="n">
-        <v>14915400</v>
+        <v>6446500</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="B205" t="n">
-        <v>48.2880859375</v>
+        <v>43.99802780151367</v>
       </c>
       <c r="C205" t="n">
-        <v>50.13380665002597</v>
+        <v>46.68181025725651</v>
       </c>
       <c r="D205" t="n">
-        <v>48.04863921622764</v>
+        <v>43.79849329826099</v>
       </c>
       <c r="E205" t="n">
-        <v>50.08392302647488</v>
+        <v>45.91359024092827</v>
       </c>
       <c r="F205" t="n">
-        <v>10979400</v>
+        <v>18546300</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="B206" t="n">
-        <v>48.53750610351562</v>
+        <v>44.75627136230469</v>
       </c>
       <c r="C206" t="n">
-        <v>49.83449929826048</v>
+        <v>45.35488246706102</v>
       </c>
       <c r="D206" t="n">
-        <v>48.48761867589451</v>
+        <v>43.99802657001164</v>
       </c>
       <c r="E206" t="n">
-        <v>48.98646250509456</v>
+        <v>44.21751908449804</v>
       </c>
       <c r="F206" t="n">
-        <v>9369900</v>
+        <v>11343400</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B207" t="n">
-        <v>48.36790084838867</v>
+        <v>44.25742721557617</v>
       </c>
       <c r="C207" t="n">
-        <v>48.90665313772215</v>
+        <v>45.0156681970104</v>
       </c>
       <c r="D207" t="n">
-        <v>48.1284579237138</v>
+        <v>43.92818844600993</v>
       </c>
       <c r="E207" t="n">
-        <v>48.63727699305541</v>
+        <v>44.81612989477721</v>
       </c>
       <c r="F207" t="n">
-        <v>4448400</v>
+        <v>7037600</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="B208" t="n">
-        <v>47.08087921142578</v>
+        <v>43.43932342529297</v>
       </c>
       <c r="C208" t="n">
-        <v>48.81685741095061</v>
+        <v>44.63654942795333</v>
       </c>
       <c r="D208" t="n">
-        <v>46.5121975508296</v>
+        <v>43.36948559067647</v>
       </c>
       <c r="E208" t="n">
-        <v>48.16835891089288</v>
+        <v>44.16763499049119</v>
       </c>
       <c r="F208" t="n">
-        <v>10210700</v>
+        <v>7527400</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="B209" t="n">
-        <v>48.16836166381836</v>
+        <v>44.83608245849609</v>
       </c>
       <c r="C209" t="n">
-        <v>48.93658166109746</v>
+        <v>45.2451342504028</v>
       </c>
       <c r="D209" t="n">
-        <v>47.19062815979313</v>
+        <v>43.89825742009147</v>
       </c>
       <c r="E209" t="n">
-        <v>47.35025804196303</v>
+        <v>43.96809525242605</v>
       </c>
       <c r="F209" t="n">
-        <v>10526700</v>
+        <v>6614900</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="B210" t="n">
-        <v>47.68947219848633</v>
+        <v>44.20754241943359</v>
       </c>
       <c r="C210" t="n">
-        <v>48.51755483192884</v>
+        <v>44.945829170483</v>
       </c>
       <c r="D210" t="n">
-        <v>47.26046617492301</v>
+        <v>44.20754241943359</v>
       </c>
       <c r="E210" t="n">
-        <v>48.51755483192884</v>
+        <v>44.66647783828879</v>
       </c>
       <c r="F210" t="n">
-        <v>5113600</v>
+        <v>4182700</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="B211" t="n">
-        <v>48.07856750488281</v>
+        <v>45.41474533081055</v>
       </c>
       <c r="C211" t="n">
-        <v>48.39782725519584</v>
+        <v>46.46231667239908</v>
       </c>
       <c r="D211" t="n">
-        <v>47.50988583677047</v>
+        <v>44.60661690999143</v>
       </c>
       <c r="E211" t="n">
-        <v>47.76928676257256</v>
+        <v>44.70638796520919</v>
       </c>
       <c r="F211" t="n">
-        <v>5188300</v>
+        <v>10953200</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="B212" t="n">
-        <v>47.1806526184082</v>
+        <v>44.05788803100586</v>
       </c>
       <c r="C212" t="n">
-        <v>47.88900997758291</v>
+        <v>45.17529717290641</v>
       </c>
       <c r="D212" t="n">
-        <v>46.90129747220957</v>
+        <v>43.91821236400285</v>
       </c>
       <c r="E212" t="n">
-        <v>47.58970442639833</v>
+        <v>45.01566729549204</v>
       </c>
       <c r="F212" t="n">
-        <v>6446500</v>
+        <v>6362800</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="B213" t="n">
-        <v>43.99802780151367</v>
+        <v>43.28966903686523</v>
       </c>
       <c r="C213" t="n">
-        <v>46.68181025725651</v>
+        <v>44.01798060692746</v>
       </c>
       <c r="D213" t="n">
-        <v>43.79849329826099</v>
+        <v>42.94047986145066</v>
       </c>
       <c r="E213" t="n">
-        <v>45.91359024092827</v>
+        <v>43.90823435011814</v>
       </c>
       <c r="F213" t="n">
-        <v>18546300</v>
+        <v>7511100</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="B214" t="n">
-        <v>44.75627136230469</v>
+        <v>43.20985412597656</v>
       </c>
       <c r="C214" t="n">
-        <v>45.35488246706102</v>
+        <v>43.39941341214399</v>
       </c>
       <c r="D214" t="n">
-        <v>43.99802657001164</v>
+        <v>42.09244120134093</v>
       </c>
       <c r="E214" t="n">
-        <v>44.21751908449804</v>
+        <v>43.27969195803174</v>
       </c>
       <c r="F214" t="n">
-        <v>11343400</v>
+        <v>9255500</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="B215" t="n">
-        <v>44.25742721557617</v>
+        <v>43.6189079284668</v>
       </c>
       <c r="C215" t="n">
-        <v>45.0156681970104</v>
+        <v>44.36717371147091</v>
       </c>
       <c r="D215" t="n">
-        <v>43.92818844600993</v>
+        <v>43.47923225791295</v>
       </c>
       <c r="E215" t="n">
-        <v>44.81612989477721</v>
+        <v>43.75858359902065</v>
       </c>
       <c r="F215" t="n">
-        <v>7037600</v>
+        <v>7130800</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="B216" t="n">
-        <v>43.43932342529297</v>
+        <v>43.03026962280273</v>
       </c>
       <c r="C216" t="n">
-        <v>44.63654942795333</v>
+        <v>43.39941298948168</v>
       </c>
       <c r="D216" t="n">
-        <v>43.36948559067647</v>
+        <v>42.73096408749883</v>
       </c>
       <c r="E216" t="n">
-        <v>44.16763499049119</v>
+        <v>43.03026962280273</v>
       </c>
       <c r="F216" t="n">
-        <v>7527400</v>
+        <v>5283900</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="B217" t="n">
-        <v>44.83608245849609</v>
+        <v>42.24209594726562</v>
       </c>
       <c r="C217" t="n">
-        <v>45.2451342504028</v>
+        <v>43.16994578148015</v>
       </c>
       <c r="D217" t="n">
-        <v>43.89825742009147</v>
+        <v>41.91285719053564</v>
       </c>
       <c r="E217" t="n">
-        <v>43.96809525242605</v>
+        <v>43.16994578148015</v>
       </c>
       <c r="F217" t="n">
-        <v>6614900</v>
+        <v>6993100</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="B218" t="n">
-        <v>44.20754241943359</v>
+        <v>41.72330093383789</v>
       </c>
       <c r="C218" t="n">
-        <v>44.945829170483</v>
+        <v>42.32191205479149</v>
       </c>
       <c r="D218" t="n">
-        <v>44.20754241943359</v>
+        <v>41.41401636468174</v>
       </c>
       <c r="E218" t="n">
-        <v>44.66647783828879</v>
+        <v>42.09244433156339</v>
       </c>
       <c r="F218" t="n">
-        <v>4182700</v>
+        <v>6814600</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="B219" t="n">
-        <v>45.41474533081055</v>
+        <v>42.48154449462891</v>
       </c>
       <c r="C219" t="n">
-        <v>46.46231667239908</v>
+        <v>42.80080425717848</v>
       </c>
       <c r="D219" t="n">
-        <v>44.60661690999143</v>
+        <v>41.71332450165757</v>
       </c>
       <c r="E219" t="n">
-        <v>44.70638796520919</v>
+        <v>42.15230572369409</v>
       </c>
       <c r="F219" t="n">
-        <v>10953200</v>
+        <v>6975500</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B220" t="n">
-        <v>44.05788803100586</v>
+        <v>42.37179946899414</v>
       </c>
       <c r="C220" t="n">
-        <v>45.17529717290641</v>
+        <v>42.73096766376914</v>
       </c>
       <c r="D220" t="n">
-        <v>43.91821236400285</v>
+        <v>41.83304717683164</v>
       </c>
       <c r="E220" t="n">
-        <v>45.01566729549204</v>
+        <v>42.0226064770177</v>
       </c>
       <c r="F220" t="n">
-        <v>6362800</v>
+        <v>3527300</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B221" t="n">
-        <v>43.28966903686523</v>
+        <v>42.63119506835938</v>
       </c>
       <c r="C221" t="n">
-        <v>44.01798060692746</v>
+        <v>43.16994734108486</v>
       </c>
       <c r="D221" t="n">
-        <v>42.94047986145066</v>
+        <v>41.95276712623318</v>
       </c>
       <c r="E221" t="n">
-        <v>43.90823435011814</v>
+        <v>42.04255917168743</v>
       </c>
       <c r="F221" t="n">
-        <v>7511100</v>
+        <v>4827600</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B222" t="n">
         <v>43.20985412597656</v>
       </c>
       <c r="C222" t="n">
-        <v>43.39941341214399</v>
+        <v>43.41936762214209</v>
       </c>
       <c r="D222" t="n">
-        <v>42.09244120134093</v>
+        <v>42.90056957982049</v>
       </c>
       <c r="E222" t="n">
-        <v>43.27969195803174</v>
+        <v>43.16994570598035</v>
       </c>
       <c r="F222" t="n">
-        <v>9255500</v>
+        <v>2514500</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B223" t="n">
-        <v>43.6189079284668</v>
+        <v>43.33955383300781</v>
       </c>
       <c r="C223" t="n">
-        <v>44.36717371147091</v>
+        <v>43.33955383300781</v>
       </c>
       <c r="D223" t="n">
-        <v>43.47923225791295</v>
+        <v>42.5613586176831</v>
       </c>
       <c r="E223" t="n">
-        <v>43.75858359902065</v>
+        <v>42.90057259977686</v>
       </c>
       <c r="F223" t="n">
-        <v>7130800</v>
+        <v>3932200</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B224" t="n">
-        <v>43.03026962280273</v>
+        <v>43.34953308105469</v>
       </c>
       <c r="C224" t="n">
-        <v>43.39941298948168</v>
+        <v>44.25742877257314</v>
       </c>
       <c r="D224" t="n">
-        <v>42.73096408749883</v>
+        <v>43.29964945521061</v>
       </c>
       <c r="E224" t="n">
-        <v>43.03026962280273</v>
+        <v>44.07784467483307</v>
       </c>
       <c r="F224" t="n">
-        <v>5283900</v>
+        <v>3920700</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B225" t="n">
-        <v>42.24209594726562</v>
+        <v>43.6189079284668</v>
       </c>
       <c r="C225" t="n">
-        <v>43.16994578148015</v>
+        <v>43.8982592695745</v>
       </c>
       <c r="D225" t="n">
-        <v>41.91285719053564</v>
+        <v>43.17992290001004</v>
       </c>
       <c r="E225" t="n">
-        <v>43.16994578148015</v>
+        <v>43.78851301246031</v>
       </c>
       <c r="F225" t="n">
-        <v>6993100</v>
+        <v>4259200</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B226" t="n">
-        <v>41.72330093383789</v>
+        <v>43.99802780151367</v>
       </c>
       <c r="C226" t="n">
-        <v>42.32191205479149</v>
+        <v>44.19756611064305</v>
       </c>
       <c r="D226" t="n">
-        <v>41.41401636468174</v>
+        <v>43.00034006174351</v>
       </c>
       <c r="E226" t="n">
-        <v>42.09244433156339</v>
+        <v>43.49918393162859</v>
       </c>
       <c r="F226" t="n">
-        <v>6814600</v>
+        <v>25788200</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B227" t="n">
-        <v>42.48154449462891</v>
+        <v>42.90056991577148</v>
       </c>
       <c r="C227" t="n">
-        <v>42.80080425717848</v>
+        <v>44.75626959548695</v>
       </c>
       <c r="D227" t="n">
-        <v>41.71332450165757</v>
+        <v>42.74094004041297</v>
       </c>
       <c r="E227" t="n">
-        <v>42.15230572369409</v>
+        <v>44.44698504690889</v>
       </c>
       <c r="F227" t="n">
-        <v>6975500</v>
+        <v>10985100</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="B228" t="n">
-        <v>42.37179946899414</v>
+        <v>41.90288162231445</v>
       </c>
       <c r="C228" t="n">
-        <v>42.73096766376914</v>
+        <v>43.25973744569153</v>
       </c>
       <c r="D228" t="n">
-        <v>41.83304717683164</v>
+        <v>41.5337382546204</v>
       </c>
       <c r="E228" t="n">
-        <v>42.0226064770177</v>
+        <v>42.7808478267131</v>
       </c>
       <c r="F228" t="n">
-        <v>3527300</v>
+        <v>9991100</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="B229" t="n">
-        <v>42.63119506835938</v>
+        <v>41.68339157104492</v>
       </c>
       <c r="C229" t="n">
-        <v>43.16994734108486</v>
+        <v>42.35184432005241</v>
       </c>
       <c r="D229" t="n">
-        <v>41.95276712623318</v>
+        <v>41.1945267213264</v>
       </c>
       <c r="E229" t="n">
-        <v>42.04255917168743</v>
+        <v>41.50380747763256</v>
       </c>
       <c r="F229" t="n">
-        <v>4827600</v>
+        <v>6573100</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46167</v>
+        <v>46178</v>
       </c>
       <c r="B230" t="n">
-        <v>43.20985412597656</v>
+        <v>42.36182022094727</v>
       </c>
       <c r="C230" t="n">
-        <v>43.41936762214209</v>
+        <v>42.56135852868104</v>
       </c>
       <c r="D230" t="n">
-        <v>42.90056957982049</v>
+        <v>41.42399512223818</v>
       </c>
       <c r="E230" t="n">
-        <v>43.16994570598035</v>
+        <v>41.82306793182907</v>
       </c>
       <c r="F230" t="n">
-        <v>2514500</v>
+        <v>10064100</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46181</v>
       </c>
       <c r="B231" t="n">
-        <v>43.33955383300781</v>
+        <v>43.89825820922852</v>
       </c>
       <c r="C231" t="n">
-        <v>43.33955383300781</v>
+        <v>44.25742638533517</v>
       </c>
       <c r="D231" t="n">
-        <v>42.5613586176831</v>
+        <v>42.22214259131513</v>
       </c>
       <c r="E231" t="n">
-        <v>42.90057259977686</v>
+        <v>42.45161030252182</v>
       </c>
       <c r="F231" t="n">
-        <v>3932200</v>
+        <v>9657900</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="B232" t="n">
-        <v>43.34953308105469</v>
+        <v>43.22980880737305</v>
       </c>
       <c r="C232" t="n">
-        <v>44.25742877257314</v>
+        <v>44.0678628011737</v>
       </c>
       <c r="D232" t="n">
-        <v>43.29964945521061</v>
+        <v>42.68107754113245</v>
       </c>
       <c r="E232" t="n">
-        <v>44.07784467483307</v>
+        <v>43.98804976618736</v>
       </c>
       <c r="F232" t="n">
-        <v>3920700</v>
+        <v>9564900</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="B233" t="n">
-        <v>43.6189079284668</v>
+        <v>42.2919807434082</v>
       </c>
       <c r="C233" t="n">
-        <v>43.8982592695745</v>
+        <v>43.12006335632115</v>
       </c>
       <c r="D233" t="n">
-        <v>43.17992290001004</v>
+        <v>41.97272098577048</v>
       </c>
       <c r="E233" t="n">
-        <v>43.78851301246031</v>
+        <v>43.03027131161826</v>
       </c>
       <c r="F233" t="n">
-        <v>4259200</v>
+        <v>7939100</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="B234" t="n">
-        <v>43.99802780151367</v>
+        <v>42.25207138061523</v>
       </c>
       <c r="C234" t="n">
-        <v>44.19756611064305</v>
+        <v>42.69105639199138</v>
       </c>
       <c r="D234" t="n">
-        <v>43.00034006174351</v>
+        <v>41.58362246729455</v>
       </c>
       <c r="E234" t="n">
-        <v>43.49918393162859</v>
+        <v>42.01262847066137</v>
       </c>
       <c r="F234" t="n">
-        <v>25788200</v>
+        <v>9103200</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="B235" t="n">
-        <v>42.90056991577148</v>
+        <v>42.511474609375</v>
       </c>
       <c r="C235" t="n">
-        <v>44.75626959548695</v>
+        <v>43.13003993378515</v>
       </c>
       <c r="D235" t="n">
-        <v>42.74094004041297</v>
+        <v>41.76320881495289</v>
       </c>
       <c r="E235" t="n">
-        <v>44.44698504690889</v>
+        <v>41.76320881495289</v>
       </c>
       <c r="F235" t="n">
-        <v>10985100</v>
+        <v>5024100</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46188</v>
       </c>
       <c r="B236" t="n">
-        <v>41.90288162231445</v>
+        <v>42.68107986450195</v>
       </c>
       <c r="C236" t="n">
-        <v>43.25973744569153</v>
+        <v>43.85835169017852</v>
       </c>
       <c r="D236" t="n">
-        <v>41.5337382546204</v>
+        <v>42.35184489271195</v>
       </c>
       <c r="E236" t="n">
-        <v>42.7808478267131</v>
+        <v>43.1699485267073</v>
       </c>
       <c r="F236" t="n">
-        <v>9991100</v>
+        <v>6230000</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="B237" t="n">
-        <v>41.68339157104492</v>
+        <v>42.73096466064453</v>
       </c>
       <c r="C237" t="n">
-        <v>42.35184432005241</v>
+        <v>42.97040756974874</v>
       </c>
       <c r="D237" t="n">
-        <v>41.1945267213264</v>
+        <v>42.08246615389085</v>
       </c>
       <c r="E237" t="n">
-        <v>41.50380747763256</v>
+        <v>42.68107723252777</v>
       </c>
       <c r="F237" t="n">
-        <v>6573100</v>
+        <v>5226700</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="B238" t="n">
-        <v>42.36182022094727</v>
+        <v>43.6987190246582</v>
       </c>
       <c r="C238" t="n">
-        <v>42.56135852868104</v>
+        <v>44.28735490003577</v>
       </c>
       <c r="D238" t="n">
-        <v>41.42399512223818</v>
+        <v>42.50149306387105</v>
       </c>
       <c r="E238" t="n">
-        <v>41.82306793182907</v>
+        <v>42.52144727390308</v>
       </c>
       <c r="F238" t="n">
-        <v>10064100</v>
+        <v>9704200</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="B239" t="n">
-        <v>43.89825820922852</v>
+        <v>45.70407485961914</v>
       </c>
       <c r="C239" t="n">
-        <v>44.25742638533517</v>
+        <v>46.12310186636294</v>
       </c>
       <c r="D239" t="n">
-        <v>42.22214259131513</v>
+        <v>43.70869946169277</v>
       </c>
       <c r="E239" t="n">
-        <v>42.45161030252182</v>
+        <v>43.70869946169277</v>
       </c>
       <c r="F239" t="n">
-        <v>9657900</v>
+        <v>16176500</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46182</v>
+        <v>46192</v>
       </c>
       <c r="B240" t="n">
-        <v>43.22980880737305</v>
+        <v>45.05557632446289</v>
       </c>
       <c r="C240" t="n">
-        <v>44.0678628011737</v>
+        <v>46.09317244459969</v>
       </c>
       <c r="D240" t="n">
-        <v>42.68107754113245</v>
+        <v>44.74629176772696</v>
       </c>
       <c r="E240" t="n">
-        <v>43.98804976618736</v>
+        <v>45.94351776743277</v>
       </c>
       <c r="F240" t="n">
-        <v>9564900</v>
+        <v>10422100</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="B241" t="n">
-        <v>42.2919807434082</v>
+        <v>45.25</v>
       </c>
       <c r="C241" t="n">
-        <v>43.12006335632115</v>
+        <v>45.79999923706055</v>
       </c>
       <c r="D241" t="n">
-        <v>41.97272098577048</v>
+        <v>44.61000061035156</v>
       </c>
       <c r="E241" t="n">
-        <v>43.03027131161826</v>
+        <v>45.02000045776367</v>
       </c>
       <c r="F241" t="n">
-        <v>7939100</v>
+        <v>5109100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="B242" t="n">
-        <v>42.25207138061523</v>
+        <v>45.70999908447266</v>
       </c>
       <c r="C242" t="n">
-        <v>42.69105639199138</v>
+        <v>46.13999938964844</v>
       </c>
       <c r="D242" t="n">
-        <v>41.58362246729455</v>
+        <v>44.43000030517578</v>
       </c>
       <c r="E242" t="n">
-        <v>42.01262847066137</v>
+        <v>44.95999908447266</v>
       </c>
       <c r="F242" t="n">
-        <v>9103200</v>
+        <v>8107300</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="B243" t="n">
-        <v>42.511474609375</v>
+        <v>46.61000061035156</v>
       </c>
       <c r="C243" t="n">
-        <v>43.13003993378515</v>
+        <v>46.61000061035156</v>
       </c>
       <c r="D243" t="n">
-        <v>41.76320881495289</v>
+        <v>45.38000106811523</v>
       </c>
       <c r="E243" t="n">
-        <v>41.76320881495289</v>
+        <v>45.52999877929688</v>
       </c>
       <c r="F243" t="n">
-        <v>5024100</v>
+        <v>9621200</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="B244" t="n">
-        <v>42.68107986450195</v>
+        <v>46.5</v>
       </c>
       <c r="C244" t="n">
-        <v>43.85835169017852</v>
+        <v>47.36999893188477</v>
       </c>
       <c r="D244" t="n">
-        <v>42.35184489271195</v>
+        <v>46.22999954223633</v>
       </c>
       <c r="E244" t="n">
-        <v>43.1699485267073</v>
+        <v>46.88999938964844</v>
       </c>
       <c r="F244" t="n">
-        <v>6230000</v>
+        <v>7163600</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="B245" t="n">
-        <v>42.73096466064453</v>
+        <v>46.90000152587891</v>
       </c>
       <c r="C245" t="n">
-        <v>42.97040756974874</v>
+        <v>47.31999969482422</v>
       </c>
       <c r="D245" t="n">
-        <v>42.08246615389085</v>
+        <v>46.18000030517578</v>
       </c>
       <c r="E245" t="n">
-        <v>42.68107723252777</v>
+        <v>46.59999847412109</v>
       </c>
       <c r="F245" t="n">
-        <v>5226700</v>
+        <v>6014600</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="B246" t="n">
-        <v>43.6987190246582</v>
+        <v>46.79000091552734</v>
       </c>
       <c r="C246" t="n">
-        <v>44.28735490003577</v>
+        <v>46.90000152587891</v>
       </c>
       <c r="D246" t="n">
-        <v>42.50149306387105</v>
+        <v>46.0099983215332</v>
       </c>
       <c r="E246" t="n">
-        <v>42.52144727390308</v>
+        <v>46.90000152587891</v>
       </c>
       <c r="F246" t="n">
-        <v>9704200</v>
+        <v>3248800</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>45.70407485961914</v>
+        <v>46.90999984741211</v>
       </c>
       <c r="C247" t="n">
-        <v>46.12310186636294</v>
+        <v>47.13999938964844</v>
       </c>
       <c r="D247" t="n">
-        <v>43.70869946169277</v>
+        <v>46.18000030517578</v>
       </c>
       <c r="E247" t="n">
-        <v>43.70869946169277</v>
+        <v>46.25</v>
       </c>
       <c r="F247" t="n">
-        <v>16176500</v>
+        <v>6927400</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46192</v>
+        <v>46204</v>
       </c>
       <c r="B248" t="n">
-        <v>45.05557632446289</v>
+        <v>46.2599983215332</v>
       </c>
       <c r="C248" t="n">
-        <v>46.09317244459969</v>
+        <v>47.13000106811523</v>
       </c>
       <c r="D248" t="n">
-        <v>44.74629176772696</v>
+        <v>46.09999847412109</v>
       </c>
       <c r="E248" t="n">
-        <v>45.94351776743277</v>
+        <v>46.90999984741211</v>
       </c>
       <c r="F248" t="n">
-        <v>10422100</v>
+        <v>4539000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="B249" t="n">
-        <v>45.25</v>
+        <v>46.2599983215332</v>
       </c>
       <c r="C249" t="n">
-        <v>45.79999923706055</v>
+        <v>46.45000076293945</v>
       </c>
       <c r="D249" t="n">
-        <v>44.61000061035156</v>
+        <v>45.90999984741211</v>
       </c>
       <c r="E249" t="n">
-        <v>45.02000045776367</v>
+        <v>46.40000152587891</v>
       </c>
       <c r="F249" t="n">
-        <v>5109100</v>
+        <v>7406500</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46206</v>
       </c>
       <c r="B250" t="n">
-        <v>45.70999908447266</v>
+        <v>46.47999954223633</v>
       </c>
       <c r="C250" t="n">
-        <v>46.13999938964844</v>
+        <v>46.90000152587891</v>
       </c>
       <c r="D250" t="n">
-        <v>44.43000030517578</v>
+        <v>46.27000045776367</v>
       </c>
       <c r="E250" t="n">
-        <v>44.95999908447266</v>
+        <v>46.29999923706055</v>
       </c>
       <c r="F250" t="n">
-        <v>8107300</v>
+        <v>2348100</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="B251" t="n">
-        <v>46.61000061035156</v>
+        <v>46.2599983215332</v>
       </c>
       <c r="C251" t="n">
-        <v>46.61000061035156</v>
+        <v>46.54999923706055</v>
       </c>
       <c r="D251" t="n">
-        <v>45.38000106811523</v>
+        <v>45.77000045776367</v>
       </c>
       <c r="E251" t="n">
-        <v>45.52999877929688</v>
+        <v>46.20000076293945</v>
       </c>
       <c r="F251" t="n">
-        <v>9621200</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B252" t="n">
-        <v>46.33000183105469</v>
-      </c>
-      <c r="C252" t="n">
-        <v>47.36999893188477</v>
-      </c>
-      <c r="D252" t="n">
-        <v>46.22999954223633</v>
-      </c>
-      <c r="E252" t="n">
-        <v>46.88999938964844</v>
-      </c>
-      <c r="F252" t="n">
-        <v>5866000</v>
+        <v>3592400</v>
       </c>
     </row>
   </sheetData>
